--- a/novo projeto/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-17).xlsx
+++ b/novo projeto/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-17).xlsx
@@ -935,13 +935,13 @@
     <t>214</t>
   </si>
   <si>
-    <t>55</t>
-  </si>
-  <si>
-    <t>R$ 4.573,55</t>
-  </si>
-  <si>
-    <t>49.8</t>
+    <t>37</t>
+  </si>
+  <si>
+    <t>R$ 4.490,46</t>
+  </si>
+  <si>
+    <t>49.1</t>
   </si>
   <si>
     <t>32.0</t>
@@ -953,13 +953,13 @@
     <t>18.0</t>
   </si>
   <si>
-    <t>6.8</t>
+    <t>6.9</t>
   </si>
   <si>
     <t>5.2</t>
   </si>
   <si>
-    <t>45.7%</t>
+    <t>48.8%</t>
   </si>
   <si>
     <t>19.7%</t>
@@ -5310,7 +5310,7 @@
         <v>19545</v>
       </c>
       <c r="B27" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C27" s="4">
         <v>51</v>
@@ -5340,14 +5340,26 @@
         <v>58</v>
       </c>
       <c r="L27" s="4"/>
-      <c r="M27" s="5"/>
-      <c r="N27" s="6"/>
+      <c r="M27" s="5">
+        <v>4662.8999999999996</v>
+      </c>
+      <c r="N27" s="6">
+        <v>49</v>
+      </c>
       <c r="O27" s="6"/>
-      <c r="P27" s="7"/>
-      <c r="Q27" s="8"/>
-      <c r="R27" s="8"/>
+      <c r="P27" s="7">
+        <v>3.8006937500000002</v>
+      </c>
+      <c r="Q27" s="8">
+        <v>19.009999999999998</v>
+      </c>
+      <c r="R27" s="8">
+        <v>12.796235483870968</v>
+      </c>
       <c r="S27" s="8"/>
-      <c r="T27" s="9"/>
+      <c r="T27" s="9">
+        <v>0.43333333333333335</v>
+      </c>
       <c r="U27" s="9"/>
       <c r="V27" s="9"/>
       <c r="W27" s="9"/>
@@ -5409,7 +5421,7 @@
         <v>19546</v>
       </c>
       <c r="B28" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C28" s="4">
         <v>51</v>
@@ -5439,14 +5451,26 @@
         <v>58</v>
       </c>
       <c r="L28" s="4"/>
-      <c r="M28" s="5"/>
-      <c r="N28" s="6"/>
+      <c r="M28" s="5">
+        <v>6102.8100000000004</v>
+      </c>
+      <c r="N28" s="6">
+        <v>69</v>
+      </c>
       <c r="O28" s="6"/>
-      <c r="P28" s="7"/>
-      <c r="Q28" s="8"/>
-      <c r="R28" s="8"/>
+      <c r="P28" s="7">
+        <v>4.4909308823529415</v>
+      </c>
+      <c r="Q28" s="8">
+        <v>18.710920689655175</v>
+      </c>
+      <c r="R28" s="8">
+        <v>6.9856310344827586</v>
+      </c>
       <c r="S28" s="8"/>
-      <c r="T28" s="9"/>
+      <c r="T28" s="9">
+        <v>0.27586206896551724</v>
+      </c>
       <c r="U28" s="9"/>
       <c r="V28" s="9"/>
       <c r="W28" s="9"/>
@@ -7016,7 +7040,7 @@
         <v>19565</v>
       </c>
       <c r="B39" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C39" s="4">
         <v>51</v>
@@ -7046,14 +7070,26 @@
         <v>58</v>
       </c>
       <c r="L39" s="4"/>
-      <c r="M39" s="5"/>
-      <c r="N39" s="6"/>
+      <c r="M39" s="5">
+        <v>4815.5600000000004</v>
+      </c>
+      <c r="N39" s="6">
+        <v>58</v>
+      </c>
       <c r="O39" s="6"/>
-      <c r="P39" s="7"/>
-      <c r="Q39" s="8"/>
-      <c r="R39" s="8"/>
+      <c r="P39" s="7">
+        <v>2.2111105263157893</v>
+      </c>
+      <c r="Q39" s="8">
+        <v>11.290403030303031</v>
+      </c>
+      <c r="R39" s="8">
+        <v>3.3333347826086959</v>
+      </c>
       <c r="S39" s="8"/>
-      <c r="T39" s="9"/>
+      <c r="T39" s="9">
+        <v>0.81818181818181823</v>
+      </c>
       <c r="U39" s="9"/>
       <c r="V39" s="9"/>
       <c r="W39" s="9"/>
@@ -7429,7 +7465,7 @@
         <v>19579</v>
       </c>
       <c r="B42" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C42" s="4">
         <v>51</v>
@@ -7459,14 +7495,26 @@
         <v>58</v>
       </c>
       <c r="L42" s="4"/>
-      <c r="M42" s="5"/>
-      <c r="N42" s="6"/>
+      <c r="M42" s="5">
+        <v>5055.1099999999997</v>
+      </c>
+      <c r="N42" s="6">
+        <v>46</v>
+      </c>
       <c r="O42" s="6"/>
-      <c r="P42" s="7"/>
-      <c r="Q42" s="8"/>
-      <c r="R42" s="8"/>
+      <c r="P42" s="7">
+        <v>7.3989361702127656</v>
+      </c>
+      <c r="Q42" s="8">
+        <v>26.162963888888889</v>
+      </c>
+      <c r="R42" s="8">
+        <v>11.131480555555555</v>
+      </c>
       <c r="S42" s="8"/>
-      <c r="T42" s="9"/>
+      <c r="T42" s="9">
+        <v>0.055555555555555552</v>
+      </c>
       <c r="U42" s="9"/>
       <c r="V42" s="9"/>
       <c r="W42" s="9"/>
@@ -8563,7 +8611,7 @@
         <v>19601</v>
       </c>
       <c r="B50" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C50" s="4">
         <v>51</v>
@@ -8593,14 +8641,26 @@
         <v>58</v>
       </c>
       <c r="L50" s="4"/>
-      <c r="M50" s="5"/>
-      <c r="N50" s="6"/>
+      <c r="M50" s="5">
+        <v>6193.0500000000002</v>
+      </c>
+      <c r="N50" s="6">
+        <v>68</v>
+      </c>
       <c r="O50" s="6"/>
-      <c r="P50" s="7"/>
-      <c r="Q50" s="8"/>
-      <c r="R50" s="8"/>
+      <c r="P50" s="7">
+        <v>2.644624193548387</v>
+      </c>
+      <c r="Q50" s="8">
+        <v>15.41622894736842</v>
+      </c>
+      <c r="R50" s="8">
+        <v>4.9245605263157897</v>
+      </c>
       <c r="S50" s="8"/>
-      <c r="T50" s="9"/>
+      <c r="T50" s="9">
+        <v>0.55263157894736847</v>
+      </c>
       <c r="U50" s="9"/>
       <c r="V50" s="9"/>
       <c r="W50" s="9"/>
@@ -9230,7 +9290,7 @@
         <v>19615</v>
       </c>
       <c r="B55" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C55" s="4">
         <v>51</v>
@@ -9260,14 +9320,26 @@
         <v>58</v>
       </c>
       <c r="L55" s="4"/>
-      <c r="M55" s="5"/>
-      <c r="N55" s="6"/>
+      <c r="M55" s="5">
+        <v>3917.71</v>
+      </c>
+      <c r="N55" s="6">
+        <v>48</v>
+      </c>
       <c r="O55" s="6"/>
-      <c r="P55" s="7"/>
-      <c r="Q55" s="8"/>
-      <c r="R55" s="8"/>
+      <c r="P55" s="7">
+        <v>3.3327037735849054</v>
+      </c>
+      <c r="Q55" s="8">
+        <v>16.600876315789474</v>
+      </c>
+      <c r="R55" s="8">
+        <v>6.7692973684210527</v>
+      </c>
       <c r="S55" s="8"/>
-      <c r="T55" s="9"/>
+      <c r="T55" s="9">
+        <v>0.52631578947368418</v>
+      </c>
       <c r="U55" s="9"/>
       <c r="V55" s="9"/>
       <c r="W55" s="9"/>
@@ -11556,7 +11628,7 @@
         <v>19649</v>
       </c>
       <c r="B71" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C71" s="4">
         <v>51</v>
@@ -11584,14 +11656,26 @@
         <v>58</v>
       </c>
       <c r="L71" s="4"/>
-      <c r="M71" s="5"/>
-      <c r="N71" s="6"/>
+      <c r="M71" s="5">
+        <v>4873.5500000000002</v>
+      </c>
+      <c r="N71" s="6">
+        <v>68</v>
+      </c>
       <c r="O71" s="6"/>
-      <c r="P71" s="7"/>
-      <c r="Q71" s="8"/>
-      <c r="R71" s="8"/>
+      <c r="P71" s="7">
+        <v>2.2982046153846154</v>
+      </c>
+      <c r="Q71" s="8">
+        <v>16.266667741935485</v>
+      </c>
+      <c r="R71" s="8">
+        <v>6.5472233333333332</v>
+      </c>
       <c r="S71" s="8"/>
-      <c r="T71" s="9"/>
+      <c r="T71" s="9">
+        <v>0.41935483870967744</v>
+      </c>
       <c r="U71" s="9"/>
       <c r="V71" s="9"/>
       <c r="W71" s="9"/>
@@ -12060,7 +12144,7 @@
         <v>19657</v>
       </c>
       <c r="B75" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C75" s="4">
         <v>51</v>
@@ -12090,14 +12174,26 @@
         <v>58</v>
       </c>
       <c r="L75" s="4"/>
-      <c r="M75" s="5"/>
-      <c r="N75" s="6"/>
+      <c r="M75" s="5">
+        <v>3059.2600000000002</v>
+      </c>
+      <c r="N75" s="6">
+        <v>33</v>
+      </c>
       <c r="O75" s="6"/>
-      <c r="P75" s="7"/>
-      <c r="Q75" s="8"/>
-      <c r="R75" s="8"/>
+      <c r="P75" s="7">
+        <v>3.858853125</v>
+      </c>
+      <c r="Q75" s="8">
+        <v>19.5303</v>
+      </c>
+      <c r="R75" s="8">
+        <v>8.7257545454545458</v>
+      </c>
       <c r="S75" s="8"/>
-      <c r="T75" s="9"/>
+      <c r="T75" s="9">
+        <v>0.090909090909090912</v>
+      </c>
       <c r="U75" s="9"/>
       <c r="V75" s="9"/>
       <c r="W75" s="9"/>
@@ -14171,7 +14267,7 @@
         <v>19694</v>
       </c>
       <c r="B90" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C90" s="4">
         <v>51</v>
@@ -14201,14 +14297,26 @@
         <v>58</v>
       </c>
       <c r="L90" s="4"/>
-      <c r="M90" s="5"/>
-      <c r="N90" s="6"/>
+      <c r="M90" s="5">
+        <v>3093.0300000000002</v>
+      </c>
+      <c r="N90" s="6">
+        <v>34</v>
+      </c>
       <c r="O90" s="6"/>
-      <c r="P90" s="7"/>
-      <c r="Q90" s="8"/>
-      <c r="R90" s="8"/>
+      <c r="P90" s="7">
+        <v>4.320706060606061</v>
+      </c>
+      <c r="Q90" s="8">
+        <v>25.385508695652174</v>
+      </c>
+      <c r="R90" s="8">
+        <v>14.029708695652173</v>
+      </c>
       <c r="S90" s="8"/>
-      <c r="T90" s="9"/>
+      <c r="T90" s="9">
+        <v>0</v>
+      </c>
       <c r="U90" s="9"/>
       <c r="V90" s="9"/>
       <c r="W90" s="9"/>
@@ -14427,7 +14535,7 @@
         <v>19700</v>
       </c>
       <c r="B92" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C92" s="4">
         <v>51</v>
@@ -14457,10 +14565,16 @@
         <v>58</v>
       </c>
       <c r="L92" s="4"/>
-      <c r="M92" s="5"/>
-      <c r="N92" s="6"/>
+      <c r="M92" s="5">
+        <v>2794.5300000000002</v>
+      </c>
+      <c r="N92" s="6">
+        <v>34</v>
+      </c>
       <c r="O92" s="6"/>
-      <c r="P92" s="7"/>
+      <c r="P92" s="7">
+        <v>4.2378378378378381</v>
+      </c>
       <c r="Q92" s="8"/>
       <c r="R92" s="8"/>
       <c r="S92" s="8"/>
@@ -16852,7 +16966,7 @@
         <v>19730</v>
       </c>
       <c r="B109" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C109" s="4">
         <v>51</v>
@@ -16880,14 +16994,26 @@
         <v>58</v>
       </c>
       <c r="L109" s="4"/>
-      <c r="M109" s="5"/>
-      <c r="N109" s="6"/>
+      <c r="M109" s="5">
+        <v>4415.3500000000004</v>
+      </c>
+      <c r="N109" s="6">
+        <v>48</v>
+      </c>
       <c r="O109" s="6"/>
-      <c r="P109" s="7"/>
-      <c r="Q109" s="8"/>
-      <c r="R109" s="8"/>
+      <c r="P109" s="7">
+        <v>4.240136734693877</v>
+      </c>
+      <c r="Q109" s="8">
+        <v>19.826185714285714</v>
+      </c>
+      <c r="R109" s="8">
+        <v>8.3023857142857143</v>
+      </c>
       <c r="S109" s="8"/>
-      <c r="T109" s="9"/>
+      <c r="T109" s="9">
+        <v>0.14285714285714285</v>
+      </c>
       <c r="U109" s="9"/>
       <c r="V109" s="9"/>
       <c r="W109" s="9"/>
@@ -21575,7 +21701,7 @@
         <v>19794</v>
       </c>
       <c r="B142" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C142" s="4">
         <v>51</v>
@@ -21603,14 +21729,26 @@
         <v>58</v>
       </c>
       <c r="L142" s="4"/>
-      <c r="M142" s="5"/>
-      <c r="N142" s="6"/>
+      <c r="M142" s="5">
+        <v>5292.0500000000002</v>
+      </c>
+      <c r="N142" s="6">
+        <v>61</v>
+      </c>
       <c r="O142" s="6"/>
-      <c r="P142" s="7"/>
-      <c r="Q142" s="8"/>
-      <c r="R142" s="8"/>
+      <c r="P142" s="7">
+        <v>2.861945</v>
+      </c>
+      <c r="Q142" s="8">
+        <v>15.606250000000001</v>
+      </c>
+      <c r="R142" s="8">
+        <v>4.9469681818181819</v>
+      </c>
       <c r="S142" s="8"/>
-      <c r="T142" s="9"/>
+      <c r="T142" s="9">
+        <v>0.5</v>
+      </c>
       <c r="U142" s="9"/>
       <c r="V142" s="9"/>
       <c r="W142" s="9"/>
@@ -23649,7 +23787,7 @@
         <v>19847</v>
       </c>
       <c r="B156" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c t="s" r="C156" s="4">
         <v>51</v>
@@ -23679,30 +23817,18 @@
         <v>58</v>
       </c>
       <c r="L156" s="4"/>
-      <c r="M156" s="5">
-        <v>4394.9099999999999</v>
-      </c>
-      <c r="N156" s="6">
-        <v>45</v>
-      </c>
+      <c r="M156" s="5"/>
+      <c r="N156" s="6"/>
       <c r="O156" s="6">
         <v>34</v>
       </c>
-      <c r="P156" s="7">
-        <v>8.5931818181818187</v>
-      </c>
-      <c r="Q156" s="8">
-        <v>19.138235294117649</v>
-      </c>
-      <c r="R156" s="8">
-        <v>3.9439393939393943</v>
-      </c>
+      <c r="P156" s="7"/>
+      <c r="Q156" s="8"/>
+      <c r="R156" s="8"/>
       <c r="S156" s="8">
         <v>7</v>
       </c>
-      <c r="T156" s="9">
-        <v>0.23529411764705882</v>
-      </c>
+      <c r="T156" s="9"/>
       <c r="U156" s="9">
         <v>0.26470588235294118</v>
       </c>
@@ -24417,7 +24543,7 @@
         <v>19872</v>
       </c>
       <c r="B162" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C162" s="4">
         <v>51</v>
@@ -24447,14 +24573,26 @@
         <v>58</v>
       </c>
       <c r="L162" s="4"/>
-      <c r="M162" s="5"/>
-      <c r="N162" s="6"/>
+      <c r="M162" s="5">
+        <v>4086.5100000000002</v>
+      </c>
+      <c r="N162" s="6">
+        <v>41</v>
+      </c>
       <c r="O162" s="6"/>
-      <c r="P162" s="7"/>
-      <c r="Q162" s="8"/>
-      <c r="R162" s="8"/>
+      <c r="P162" s="7">
+        <v>8.7004175000000004</v>
+      </c>
+      <c r="Q162" s="8">
+        <v>23.43525769230769</v>
+      </c>
+      <c r="R162" s="8">
+        <v>7.2519230769230774</v>
+      </c>
       <c r="S162" s="8"/>
-      <c r="T162" s="9"/>
+      <c r="T162" s="9">
+        <v>0</v>
+      </c>
       <c r="U162" s="9"/>
       <c r="V162" s="9"/>
       <c r="W162" s="9"/>
@@ -26340,7 +26478,7 @@
         <v>19897</v>
       </c>
       <c r="B175" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C175" s="4">
         <v>51</v>
@@ -26370,14 +26508,26 @@
         <v>58</v>
       </c>
       <c r="L175" s="4"/>
-      <c r="M175" s="5"/>
-      <c r="N175" s="6"/>
+      <c r="M175" s="5">
+        <v>2719.6100000000001</v>
+      </c>
+      <c r="N175" s="6">
+        <v>34</v>
+      </c>
       <c r="O175" s="6"/>
-      <c r="P175" s="7"/>
-      <c r="Q175" s="8"/>
-      <c r="R175" s="8"/>
+      <c r="P175" s="7">
+        <v>9.9716666666666658</v>
+      </c>
+      <c r="Q175" s="8">
+        <v>18.342594444444444</v>
+      </c>
+      <c r="R175" s="8">
+        <v>1.4435166666666666</v>
+      </c>
       <c r="S175" s="8"/>
-      <c r="T175" s="9"/>
+      <c r="T175" s="9">
+        <v>0.5</v>
+      </c>
       <c r="U175" s="9"/>
       <c r="V175" s="9"/>
       <c r="W175" s="9"/>
@@ -27172,7 +27322,7 @@
         <v>19910</v>
       </c>
       <c r="B181" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C181" s="4">
         <v>51</v>
@@ -27202,14 +27352,26 @@
         <v>58</v>
       </c>
       <c r="L181" s="4"/>
-      <c r="M181" s="5"/>
-      <c r="N181" s="6"/>
+      <c r="M181" s="5">
+        <v>2344.5999999999999</v>
+      </c>
+      <c r="N181" s="6">
+        <v>28</v>
+      </c>
       <c r="O181" s="6"/>
-      <c r="P181" s="7"/>
-      <c r="Q181" s="8"/>
-      <c r="R181" s="8"/>
+      <c r="P181" s="7">
+        <v>3.0942517241379308</v>
+      </c>
+      <c r="Q181" s="8">
+        <v>9.8499999999999996</v>
+      </c>
+      <c r="R181" s="8">
+        <v>1.1694500000000001</v>
+      </c>
       <c r="S181" s="8"/>
-      <c r="T181" s="9"/>
+      <c r="T181" s="9">
+        <v>0.95238095238095233</v>
+      </c>
       <c r="U181" s="9"/>
       <c r="V181" s="9"/>
       <c r="W181" s="9"/>
@@ -27998,7 +28160,7 @@
         <v>19927</v>
       </c>
       <c r="B187" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C187" s="4">
         <v>51</v>
@@ -28028,14 +28190,26 @@
         <v>58</v>
       </c>
       <c r="L187" s="4"/>
-      <c r="M187" s="5"/>
-      <c r="N187" s="6"/>
+      <c r="M187" s="5">
+        <v>1615.6500000000001</v>
+      </c>
+      <c r="N187" s="6">
+        <v>18</v>
+      </c>
       <c r="O187" s="6"/>
-      <c r="P187" s="7"/>
-      <c r="Q187" s="8"/>
-      <c r="R187" s="8"/>
+      <c r="P187" s="7">
+        <v>9.9583333333333339</v>
+      </c>
+      <c r="Q187" s="8">
+        <v>27.887176923076922</v>
+      </c>
+      <c r="R187" s="8">
+        <v>14.256407692307693</v>
+      </c>
       <c r="S187" s="8"/>
-      <c r="T187" s="9"/>
+      <c r="T187" s="9">
+        <v>0</v>
+      </c>
       <c r="U187" s="9"/>
       <c r="V187" s="9"/>
       <c r="W187" s="9"/>
@@ -28411,7 +28585,7 @@
         <v>19931</v>
       </c>
       <c r="B190" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C190" s="4">
         <v>51</v>
@@ -28441,14 +28615,26 @@
         <v>58</v>
       </c>
       <c r="L190" s="4"/>
-      <c r="M190" s="5"/>
-      <c r="N190" s="6"/>
+      <c r="M190" s="5">
+        <v>3157.4200000000001</v>
+      </c>
+      <c r="N190" s="6">
+        <v>40</v>
+      </c>
       <c r="O190" s="6"/>
-      <c r="P190" s="7"/>
-      <c r="Q190" s="8"/>
-      <c r="R190" s="8"/>
+      <c r="P190" s="7">
+        <v>4.2000000000000002</v>
+      </c>
+      <c r="Q190" s="8">
+        <v>14.149072222222223</v>
+      </c>
+      <c r="R190" s="8">
+        <v>3.7901941176470588</v>
+      </c>
       <c r="S190" s="8"/>
-      <c r="T190" s="9"/>
+      <c r="T190" s="9">
+        <v>0.55555555555555558</v>
+      </c>
       <c r="U190" s="9"/>
       <c r="V190" s="9"/>
       <c r="W190" s="9"/>
@@ -29805,7 +29991,7 @@
         <v>19954</v>
       </c>
       <c r="B200" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C200" s="4">
         <v>51</v>
@@ -29835,14 +30021,26 @@
         <v>58</v>
       </c>
       <c r="L200" s="4"/>
-      <c r="M200" s="5"/>
-      <c r="N200" s="6"/>
+      <c r="M200" s="5">
+        <v>1226.3399999999999</v>
+      </c>
+      <c r="N200" s="6">
+        <v>14</v>
+      </c>
       <c r="O200" s="6"/>
-      <c r="P200" s="7"/>
-      <c r="Q200" s="8"/>
-      <c r="R200" s="8"/>
+      <c r="P200" s="7">
+        <v>5.148715384615385</v>
+      </c>
+      <c r="Q200" s="8">
+        <v>14.211116666666667</v>
+      </c>
+      <c r="R200" s="8">
+        <v>2.3722166666666666</v>
+      </c>
       <c r="S200" s="8"/>
-      <c r="T200" s="9"/>
+      <c r="T200" s="9">
+        <v>0.66666666666666663</v>
+      </c>
       <c r="U200" s="9"/>
       <c r="V200" s="9"/>
       <c r="W200" s="9"/>
@@ -30730,7 +30928,7 @@
         <v>19962</v>
       </c>
       <c r="B207" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C207" s="4">
         <v>51</v>
@@ -30760,14 +30958,26 @@
         <v>58</v>
       </c>
       <c r="L207" s="4"/>
-      <c r="M207" s="5"/>
-      <c r="N207" s="6"/>
+      <c r="M207" s="5">
+        <v>2587.75</v>
+      </c>
+      <c r="N207" s="6">
+        <v>27</v>
+      </c>
       <c r="O207" s="6"/>
-      <c r="P207" s="7"/>
-      <c r="Q207" s="8"/>
-      <c r="R207" s="8"/>
+      <c r="P207" s="7">
+        <v>7.7791678571428573</v>
+      </c>
+      <c r="Q207" s="8">
+        <v>21.787881818181816</v>
+      </c>
+      <c r="R207" s="8">
+        <v>7.8816699999999997</v>
+      </c>
       <c r="S207" s="8"/>
-      <c r="T207" s="9"/>
+      <c r="T207" s="9">
+        <v>0.18181818181818182</v>
+      </c>
       <c r="U207" s="9"/>
       <c r="V207" s="9"/>
       <c r="W207" s="9"/>

--- a/novo projeto/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-17).xlsx
+++ b/novo projeto/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-17).xlsx
@@ -935,88 +935,94 @@
     <t>214</t>
   </si>
   <si>
-    <t>37</t>
-  </si>
-  <si>
-    <t>R$ 4.490,46</t>
-  </si>
-  <si>
-    <t>49.1</t>
+    <t>32</t>
+  </si>
+  <si>
+    <t>R$ 4.502,58</t>
+  </si>
+  <si>
+    <t>49.2</t>
+  </si>
+  <si>
+    <t>30.9</t>
+  </si>
+  <si>
+    <t>4.86</t>
+  </si>
+  <si>
+    <t>18.2</t>
+  </si>
+  <si>
+    <t>6.9</t>
+  </si>
+  <si>
+    <t>6.0</t>
+  </si>
+  <si>
+    <t>44.5%</t>
+  </si>
+  <si>
+    <t>19.9%</t>
+  </si>
+  <si>
+    <t>1.9%</t>
+  </si>
+  <si>
+    <t>0.5%</t>
+  </si>
+  <si>
+    <t>5.2%</t>
+  </si>
+  <si>
+    <t>1.5%</t>
+  </si>
+  <si>
+    <t>0.3%</t>
+  </si>
+  <si>
+    <t>7.7%</t>
+  </si>
+  <si>
+    <t>2.9%</t>
+  </si>
+  <si>
+    <t>4.7%</t>
+  </si>
+  <si>
+    <t>1361.0</t>
+  </si>
+  <si>
+    <t>1093.0</t>
+  </si>
+  <si>
+    <t>106.0</t>
+  </si>
+  <si>
+    <t>29.0</t>
+  </si>
+  <si>
+    <t>286.0</t>
+  </si>
+  <si>
+    <t>84.0</t>
+  </si>
+  <si>
+    <t>14.0</t>
+  </si>
+  <si>
+    <t>426.0</t>
+  </si>
+  <si>
+    <t>157.0</t>
+  </si>
+  <si>
+    <t>256.0</t>
+  </si>
+  <si>
+    <t>0.6%</t>
   </si>
   <si>
     <t>32.0</t>
-  </si>
-  <si>
-    <t>4.78</t>
-  </si>
-  <si>
-    <t>18.0</t>
-  </si>
-  <si>
-    <t>6.9</t>
-  </si>
-  <si>
-    <t>5.2</t>
-  </si>
-  <si>
-    <t>48.8%</t>
-  </si>
-  <si>
-    <t>19.7%</t>
-  </si>
-  <si>
-    <t>1.8%</t>
-  </si>
-  <si>
-    <t>0.6%</t>
-  </si>
-  <si>
-    <t>5.3%</t>
-  </si>
-  <si>
-    <t>1.6%</t>
-  </si>
-  <si>
-    <t>0.3%</t>
-  </si>
-  <si>
-    <t>7.7%</t>
-  </si>
-  <si>
-    <t>2.8%</t>
-  </si>
-  <si>
-    <t>4.5%</t>
-  </si>
-  <si>
-    <t>1217.0</t>
-  </si>
-  <si>
-    <t>976.0</t>
-  </si>
-  <si>
-    <t>89.0</t>
-  </si>
-  <si>
-    <t>29.0</t>
-  </si>
-  <si>
-    <t>261.0</t>
-  </si>
-  <si>
-    <t>77.0</t>
-  </si>
-  <si>
-    <t>14.0</t>
-  </si>
-  <si>
-    <t>383.0</t>
-  </si>
-  <si>
-    <t>139.0</t>
-  </si>
-  <si>
-    <t>222.0</t>
   </si>
   <si>
     <t>1</t>
@@ -3236,7 +3242,7 @@
         <v>19515</v>
       </c>
       <c r="B13" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C13" s="4">
         <v>51</v>
@@ -3266,14 +3272,26 @@
         <v>58</v>
       </c>
       <c r="L13" s="4"/>
-      <c r="M13" s="5"/>
-      <c r="N13" s="6"/>
+      <c r="M13" s="5">
+        <v>6454.0200000000004</v>
+      </c>
+      <c r="N13" s="6">
+        <v>66</v>
+      </c>
       <c r="O13" s="6"/>
-      <c r="P13" s="7"/>
-      <c r="Q13" s="8"/>
-      <c r="R13" s="8"/>
+      <c r="P13" s="7">
+        <v>4.879040909090909</v>
+      </c>
+      <c r="Q13" s="8">
+        <v>20.663121276595746</v>
+      </c>
+      <c r="R13" s="8">
+        <v>8.8581553191489366</v>
+      </c>
       <c r="S13" s="8"/>
-      <c r="T13" s="9"/>
+      <c r="T13" s="9">
+        <v>0.21276595744680851</v>
+      </c>
       <c r="U13" s="9"/>
       <c r="V13" s="9"/>
       <c r="W13" s="9"/>
@@ -5346,7 +5364,9 @@
       <c r="N27" s="6">
         <v>49</v>
       </c>
-      <c r="O27" s="6"/>
+      <c r="O27" s="6">
+        <v>31</v>
+      </c>
       <c r="P27" s="7">
         <v>3.8006937500000002</v>
       </c>
@@ -5356,31 +5376,75 @@
       <c r="R27" s="8">
         <v>12.796235483870968</v>
       </c>
-      <c r="S27" s="8"/>
+      <c r="S27" s="8">
+        <v>8</v>
+      </c>
       <c r="T27" s="9">
         <v>0.43333333333333335</v>
       </c>
-      <c r="U27" s="9"/>
-      <c r="V27" s="9"/>
-      <c r="W27" s="9"/>
-      <c r="X27" s="9"/>
-      <c r="Y27" s="9"/>
-      <c r="Z27" s="9"/>
-      <c r="AA27" s="9"/>
-      <c r="AB27" s="9"/>
-      <c r="AC27" s="9"/>
-      <c r="AD27" s="6"/>
-      <c r="AE27" s="6"/>
-      <c r="AF27" s="6"/>
-      <c r="AG27" s="6"/>
-      <c r="AH27" s="6"/>
-      <c r="AI27" s="6"/>
-      <c r="AJ27" s="6"/>
-      <c r="AK27" s="6"/>
-      <c r="AL27" s="6"/>
-      <c r="AM27" s="6"/>
-      <c r="AN27" s="9"/>
-      <c r="AO27" s="6"/>
+      <c r="U27" s="9">
+        <v>0.16129032258064516</v>
+      </c>
+      <c r="V27" s="9">
+        <v>0.032258064516129031</v>
+      </c>
+      <c r="W27" s="9">
+        <v>0</v>
+      </c>
+      <c r="X27" s="9">
+        <v>0.12903225806451613</v>
+      </c>
+      <c r="Y27" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z27" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA27" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB27" s="9">
+        <v>0.032258064516129031</v>
+      </c>
+      <c r="AC27" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD27" s="6">
+        <v>6</v>
+      </c>
+      <c r="AE27" s="6">
+        <v>5</v>
+      </c>
+      <c r="AF27" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG27" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH27" s="6">
+        <v>4</v>
+      </c>
+      <c r="AI27" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ27" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK27" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL27" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM27" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN27" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO27" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP27" s="4">
         <v>58</v>
       </c>
@@ -5457,7 +5521,9 @@
       <c r="N28" s="6">
         <v>69</v>
       </c>
-      <c r="O28" s="6"/>
+      <c r="O28" s="6">
+        <v>29</v>
+      </c>
       <c r="P28" s="7">
         <v>4.4909308823529415</v>
       </c>
@@ -5467,31 +5533,75 @@
       <c r="R28" s="8">
         <v>6.9856310344827586</v>
       </c>
-      <c r="S28" s="8"/>
+      <c r="S28" s="8">
+        <v>7</v>
+      </c>
       <c r="T28" s="9">
         <v>0.27586206896551724</v>
       </c>
-      <c r="U28" s="9"/>
-      <c r="V28" s="9"/>
-      <c r="W28" s="9"/>
-      <c r="X28" s="9"/>
-      <c r="Y28" s="9"/>
-      <c r="Z28" s="9"/>
-      <c r="AA28" s="9"/>
-      <c r="AB28" s="9"/>
-      <c r="AC28" s="9"/>
-      <c r="AD28" s="6"/>
-      <c r="AE28" s="6"/>
-      <c r="AF28" s="6"/>
-      <c r="AG28" s="6"/>
-      <c r="AH28" s="6"/>
-      <c r="AI28" s="6"/>
-      <c r="AJ28" s="6"/>
-      <c r="AK28" s="6"/>
-      <c r="AL28" s="6"/>
-      <c r="AM28" s="6"/>
-      <c r="AN28" s="9"/>
-      <c r="AO28" s="6"/>
+      <c r="U28" s="9">
+        <v>0.068965517241379309</v>
+      </c>
+      <c r="V28" s="9">
+        <v>0</v>
+      </c>
+      <c r="W28" s="9">
+        <v>0</v>
+      </c>
+      <c r="X28" s="9">
+        <v>0.034482758620689655</v>
+      </c>
+      <c r="Y28" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z28" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA28" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB28" s="9">
+        <v>0.034482758620689655</v>
+      </c>
+      <c r="AC28" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD28" s="6">
+        <v>2</v>
+      </c>
+      <c r="AE28" s="6">
+        <v>2</v>
+      </c>
+      <c r="AF28" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG28" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH28" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI28" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ28" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK28" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL28" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM28" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN28" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO28" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP28" s="4">
         <v>58</v>
       </c>
@@ -7076,7 +7186,9 @@
       <c r="N39" s="6">
         <v>58</v>
       </c>
-      <c r="O39" s="6"/>
+      <c r="O39" s="6">
+        <v>33</v>
+      </c>
       <c r="P39" s="7">
         <v>2.2111105263157893</v>
       </c>
@@ -7086,31 +7198,75 @@
       <c r="R39" s="8">
         <v>3.3333347826086959</v>
       </c>
-      <c r="S39" s="8"/>
+      <c r="S39" s="8">
+        <v>8</v>
+      </c>
       <c r="T39" s="9">
         <v>0.81818181818181823</v>
       </c>
-      <c r="U39" s="9"/>
-      <c r="V39" s="9"/>
-      <c r="W39" s="9"/>
-      <c r="X39" s="9"/>
-      <c r="Y39" s="9"/>
-      <c r="Z39" s="9"/>
-      <c r="AA39" s="9"/>
-      <c r="AB39" s="9"/>
-      <c r="AC39" s="9"/>
-      <c r="AD39" s="6"/>
-      <c r="AE39" s="6"/>
-      <c r="AF39" s="6"/>
-      <c r="AG39" s="6"/>
-      <c r="AH39" s="6"/>
-      <c r="AI39" s="6"/>
-      <c r="AJ39" s="6"/>
-      <c r="AK39" s="6"/>
-      <c r="AL39" s="6"/>
-      <c r="AM39" s="6"/>
-      <c r="AN39" s="9"/>
-      <c r="AO39" s="6"/>
+      <c r="U39" s="9">
+        <v>0.42424242424242425</v>
+      </c>
+      <c r="V39" s="9">
+        <v>0.030303030303030304</v>
+      </c>
+      <c r="W39" s="9">
+        <v>0</v>
+      </c>
+      <c r="X39" s="9">
+        <v>0.090909090909090912</v>
+      </c>
+      <c r="Y39" s="9">
+        <v>0.090909090909090912</v>
+      </c>
+      <c r="Z39" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA39" s="9">
+        <v>0.39393939393939392</v>
+      </c>
+      <c r="AB39" s="9">
+        <v>0.030303030303030304</v>
+      </c>
+      <c r="AC39" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD39" s="6">
+        <v>21</v>
+      </c>
+      <c r="AE39" s="6">
+        <v>14</v>
+      </c>
+      <c r="AF39" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG39" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH39" s="6">
+        <v>3</v>
+      </c>
+      <c r="AI39" s="6">
+        <v>3</v>
+      </c>
+      <c r="AJ39" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK39" s="6">
+        <v>13</v>
+      </c>
+      <c r="AL39" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM39" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN39" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO39" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP39" s="4">
         <v>58</v>
       </c>
@@ -7501,7 +7657,9 @@
       <c r="N42" s="6">
         <v>46</v>
       </c>
-      <c r="O42" s="6"/>
+      <c r="O42" s="6">
+        <v>36</v>
+      </c>
       <c r="P42" s="7">
         <v>7.3989361702127656</v>
       </c>
@@ -7511,31 +7669,75 @@
       <c r="R42" s="8">
         <v>11.131480555555555</v>
       </c>
-      <c r="S42" s="8"/>
+      <c r="S42" s="8">
+        <v>7</v>
+      </c>
       <c r="T42" s="9">
         <v>0.055555555555555552</v>
       </c>
-      <c r="U42" s="9"/>
-      <c r="V42" s="9"/>
-      <c r="W42" s="9"/>
-      <c r="X42" s="9"/>
-      <c r="Y42" s="9"/>
-      <c r="Z42" s="9"/>
-      <c r="AA42" s="9"/>
-      <c r="AB42" s="9"/>
-      <c r="AC42" s="9"/>
-      <c r="AD42" s="6"/>
-      <c r="AE42" s="6"/>
-      <c r="AF42" s="6"/>
-      <c r="AG42" s="6"/>
-      <c r="AH42" s="6"/>
-      <c r="AI42" s="6"/>
-      <c r="AJ42" s="6"/>
-      <c r="AK42" s="6"/>
-      <c r="AL42" s="6"/>
-      <c r="AM42" s="6"/>
-      <c r="AN42" s="9"/>
-      <c r="AO42" s="6"/>
+      <c r="U42" s="9">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="V42" s="9">
+        <v>0</v>
+      </c>
+      <c r="W42" s="9">
+        <v>0</v>
+      </c>
+      <c r="X42" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y42" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC42" s="9">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="AD42" s="6">
+        <v>4</v>
+      </c>
+      <c r="AE42" s="6">
+        <v>4</v>
+      </c>
+      <c r="AF42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM42" s="6">
+        <v>4</v>
+      </c>
+      <c r="AN42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO42" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP42" s="4">
         <v>58</v>
       </c>
@@ -8047,7 +8249,7 @@
         <v>19596</v>
       </c>
       <c r="B46" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C46" s="4">
         <v>51</v>
@@ -8075,35 +8277,93 @@
         <v>58</v>
       </c>
       <c r="L46" s="4"/>
-      <c r="M46" s="5"/>
-      <c r="N46" s="6"/>
-      <c r="O46" s="6"/>
-      <c r="P46" s="7"/>
-      <c r="Q46" s="8"/>
-      <c r="R46" s="8"/>
-      <c r="S46" s="8"/>
-      <c r="T46" s="9"/>
-      <c r="U46" s="9"/>
-      <c r="V46" s="9"/>
-      <c r="W46" s="9"/>
-      <c r="X46" s="9"/>
-      <c r="Y46" s="9"/>
-      <c r="Z46" s="9"/>
-      <c r="AA46" s="9"/>
-      <c r="AB46" s="9"/>
-      <c r="AC46" s="9"/>
-      <c r="AD46" s="6"/>
-      <c r="AE46" s="6"/>
-      <c r="AF46" s="6"/>
-      <c r="AG46" s="6"/>
-      <c r="AH46" s="6"/>
-      <c r="AI46" s="6"/>
-      <c r="AJ46" s="6"/>
-      <c r="AK46" s="6"/>
-      <c r="AL46" s="6"/>
-      <c r="AM46" s="6"/>
-      <c r="AN46" s="9"/>
-      <c r="AO46" s="6"/>
+      <c r="M46" s="5">
+        <v>6231.1700000000001</v>
+      </c>
+      <c r="N46" s="6">
+        <v>67</v>
+      </c>
+      <c r="O46" s="6">
+        <v>41</v>
+      </c>
+      <c r="P46" s="7">
+        <v>9.4674353846153849</v>
+      </c>
+      <c r="Q46" s="8">
+        <v>34.68292682926829</v>
+      </c>
+      <c r="R46" s="8">
+        <v>16.091463414634145</v>
+      </c>
+      <c r="S46" s="8">
+        <v>7</v>
+      </c>
+      <c r="T46" s="9">
+        <v>0.024390243902439025</v>
+      </c>
+      <c r="U46" s="9">
+        <v>0.24390243902439024</v>
+      </c>
+      <c r="V46" s="9">
+        <v>0.097560975609756101</v>
+      </c>
+      <c r="W46" s="9">
+        <v>0</v>
+      </c>
+      <c r="X46" s="9">
+        <v>0.024390243902439025</v>
+      </c>
+      <c r="Y46" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z46" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA46" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB46" s="9">
+        <v>0.073170731707317069</v>
+      </c>
+      <c r="AC46" s="9">
+        <v>0.04878048780487805</v>
+      </c>
+      <c r="AD46" s="6">
+        <v>10</v>
+      </c>
+      <c r="AE46" s="6">
+        <v>10</v>
+      </c>
+      <c r="AF46" s="6">
+        <v>4</v>
+      </c>
+      <c r="AG46" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH46" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI46" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ46" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK46" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL46" s="6">
+        <v>3</v>
+      </c>
+      <c r="AM46" s="6">
+        <v>2</v>
+      </c>
+      <c r="AN46" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO46" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP46" s="4">
         <v>58</v>
       </c>
@@ -8647,7 +8907,9 @@
       <c r="N50" s="6">
         <v>68</v>
       </c>
-      <c r="O50" s="6"/>
+      <c r="O50" s="6">
+        <v>38</v>
+      </c>
       <c r="P50" s="7">
         <v>2.644624193548387</v>
       </c>
@@ -8657,31 +8919,75 @@
       <c r="R50" s="8">
         <v>4.9245605263157897</v>
       </c>
-      <c r="S50" s="8"/>
+      <c r="S50" s="8">
+        <v>8</v>
+      </c>
       <c r="T50" s="9">
         <v>0.55263157894736847</v>
       </c>
-      <c r="U50" s="9"/>
-      <c r="V50" s="9"/>
-      <c r="W50" s="9"/>
-      <c r="X50" s="9"/>
-      <c r="Y50" s="9"/>
-      <c r="Z50" s="9"/>
-      <c r="AA50" s="9"/>
-      <c r="AB50" s="9"/>
-      <c r="AC50" s="9"/>
-      <c r="AD50" s="6"/>
-      <c r="AE50" s="6"/>
-      <c r="AF50" s="6"/>
-      <c r="AG50" s="6"/>
-      <c r="AH50" s="6"/>
-      <c r="AI50" s="6"/>
-      <c r="AJ50" s="6"/>
-      <c r="AK50" s="6"/>
-      <c r="AL50" s="6"/>
-      <c r="AM50" s="6"/>
-      <c r="AN50" s="9"/>
-      <c r="AO50" s="6"/>
+      <c r="U50" s="9">
+        <v>0.13157894736842105</v>
+      </c>
+      <c r="V50" s="9">
+        <v>0.026315789473684209</v>
+      </c>
+      <c r="W50" s="9">
+        <v>0</v>
+      </c>
+      <c r="X50" s="9">
+        <v>0.052631578947368418</v>
+      </c>
+      <c r="Y50" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z50" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA50" s="9">
+        <v>0.078947368421052627</v>
+      </c>
+      <c r="AB50" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC50" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD50" s="6">
+        <v>6</v>
+      </c>
+      <c r="AE50" s="6">
+        <v>5</v>
+      </c>
+      <c r="AF50" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG50" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH50" s="6">
+        <v>2</v>
+      </c>
+      <c r="AI50" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ50" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK50" s="6">
+        <v>3</v>
+      </c>
+      <c r="AL50" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM50" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN50" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO50" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP50" s="4">
         <v>58</v>
       </c>
@@ -9326,7 +9632,9 @@
       <c r="N55" s="6">
         <v>48</v>
       </c>
-      <c r="O55" s="6"/>
+      <c r="O55" s="6">
+        <v>38</v>
+      </c>
       <c r="P55" s="7">
         <v>3.3327037735849054</v>
       </c>
@@ -9336,31 +9644,75 @@
       <c r="R55" s="8">
         <v>6.7692973684210527</v>
       </c>
-      <c r="S55" s="8"/>
+      <c r="S55" s="8">
+        <v>7</v>
+      </c>
       <c r="T55" s="9">
         <v>0.52631578947368418</v>
       </c>
-      <c r="U55" s="9"/>
-      <c r="V55" s="9"/>
-      <c r="W55" s="9"/>
-      <c r="X55" s="9"/>
-      <c r="Y55" s="9"/>
-      <c r="Z55" s="9"/>
-      <c r="AA55" s="9"/>
-      <c r="AB55" s="9"/>
-      <c r="AC55" s="9"/>
-      <c r="AD55" s="6"/>
-      <c r="AE55" s="6"/>
-      <c r="AF55" s="6"/>
-      <c r="AG55" s="6"/>
-      <c r="AH55" s="6"/>
-      <c r="AI55" s="6"/>
-      <c r="AJ55" s="6"/>
-      <c r="AK55" s="6"/>
-      <c r="AL55" s="6"/>
-      <c r="AM55" s="6"/>
-      <c r="AN55" s="9"/>
-      <c r="AO55" s="6"/>
+      <c r="U55" s="9">
+        <v>0.052631578947368418</v>
+      </c>
+      <c r="V55" s="9">
+        <v>0</v>
+      </c>
+      <c r="W55" s="9">
+        <v>0</v>
+      </c>
+      <c r="X55" s="9">
+        <v>0.052631578947368418</v>
+      </c>
+      <c r="Y55" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z55" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA55" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB55" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC55" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD55" s="6">
+        <v>2</v>
+      </c>
+      <c r="AE55" s="6">
+        <v>2</v>
+      </c>
+      <c r="AF55" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG55" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH55" s="6">
+        <v>2</v>
+      </c>
+      <c r="AI55" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ55" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK55" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL55" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM55" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN55" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO55" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP55" s="4">
         <v>58</v>
       </c>
@@ -11662,7 +12014,9 @@
       <c r="N71" s="6">
         <v>68</v>
       </c>
-      <c r="O71" s="6"/>
+      <c r="O71" s="6">
+        <v>31</v>
+      </c>
       <c r="P71" s="7">
         <v>2.2982046153846154</v>
       </c>
@@ -11672,31 +12026,75 @@
       <c r="R71" s="8">
         <v>6.5472233333333332</v>
       </c>
-      <c r="S71" s="8"/>
+      <c r="S71" s="8">
+        <v>8</v>
+      </c>
       <c r="T71" s="9">
         <v>0.41935483870967744</v>
       </c>
-      <c r="U71" s="9"/>
-      <c r="V71" s="9"/>
-      <c r="W71" s="9"/>
-      <c r="X71" s="9"/>
-      <c r="Y71" s="9"/>
-      <c r="Z71" s="9"/>
-      <c r="AA71" s="9"/>
-      <c r="AB71" s="9"/>
-      <c r="AC71" s="9"/>
-      <c r="AD71" s="6"/>
-      <c r="AE71" s="6"/>
-      <c r="AF71" s="6"/>
-      <c r="AG71" s="6"/>
-      <c r="AH71" s="6"/>
-      <c r="AI71" s="6"/>
-      <c r="AJ71" s="6"/>
-      <c r="AK71" s="6"/>
-      <c r="AL71" s="6"/>
-      <c r="AM71" s="6"/>
-      <c r="AN71" s="9"/>
-      <c r="AO71" s="6"/>
+      <c r="U71" s="9">
+        <v>0.29032258064516131</v>
+      </c>
+      <c r="V71" s="9">
+        <v>0.064516129032258063</v>
+      </c>
+      <c r="W71" s="9">
+        <v>0</v>
+      </c>
+      <c r="X71" s="9">
+        <v>0.064516129032258063</v>
+      </c>
+      <c r="Y71" s="9">
+        <v>0.032258064516129031</v>
+      </c>
+      <c r="Z71" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA71" s="9">
+        <v>0.096774193548387094</v>
+      </c>
+      <c r="AB71" s="9">
+        <v>0.12903225806451613</v>
+      </c>
+      <c r="AC71" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD71" s="6">
+        <v>12</v>
+      </c>
+      <c r="AE71" s="6">
+        <v>9</v>
+      </c>
+      <c r="AF71" s="6">
+        <v>2</v>
+      </c>
+      <c r="AG71" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH71" s="6">
+        <v>2</v>
+      </c>
+      <c r="AI71" s="6">
+        <v>1</v>
+      </c>
+      <c r="AJ71" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK71" s="6">
+        <v>3</v>
+      </c>
+      <c r="AL71" s="6">
+        <v>4</v>
+      </c>
+      <c r="AM71" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN71" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO71" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP71" s="4">
         <v>58</v>
       </c>
@@ -12180,7 +12578,9 @@
       <c r="N75" s="6">
         <v>33</v>
       </c>
-      <c r="O75" s="6"/>
+      <c r="O75" s="6">
+        <v>11</v>
+      </c>
       <c r="P75" s="7">
         <v>3.858853125</v>
       </c>
@@ -12190,31 +12590,75 @@
       <c r="R75" s="8">
         <v>8.7257545454545458</v>
       </c>
-      <c r="S75" s="8"/>
+      <c r="S75" s="8">
+        <v>7</v>
+      </c>
       <c r="T75" s="9">
         <v>0.090909090909090912</v>
       </c>
-      <c r="U75" s="9"/>
-      <c r="V75" s="9"/>
-      <c r="W75" s="9"/>
-      <c r="X75" s="9"/>
-      <c r="Y75" s="9"/>
-      <c r="Z75" s="9"/>
-      <c r="AA75" s="9"/>
-      <c r="AB75" s="9"/>
-      <c r="AC75" s="9"/>
-      <c r="AD75" s="6"/>
-      <c r="AE75" s="6"/>
-      <c r="AF75" s="6"/>
-      <c r="AG75" s="6"/>
-      <c r="AH75" s="6"/>
-      <c r="AI75" s="6"/>
-      <c r="AJ75" s="6"/>
-      <c r="AK75" s="6"/>
-      <c r="AL75" s="6"/>
-      <c r="AM75" s="6"/>
-      <c r="AN75" s="9"/>
-      <c r="AO75" s="6"/>
+      <c r="U75" s="9">
+        <v>0.18181818181818182</v>
+      </c>
+      <c r="V75" s="9">
+        <v>0</v>
+      </c>
+      <c r="W75" s="9">
+        <v>0</v>
+      </c>
+      <c r="X75" s="9">
+        <v>0.090909090909090912</v>
+      </c>
+      <c r="Y75" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z75" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA75" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB75" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC75" s="9">
+        <v>0.18181818181818182</v>
+      </c>
+      <c r="AD75" s="6">
+        <v>3</v>
+      </c>
+      <c r="AE75" s="6">
+        <v>2</v>
+      </c>
+      <c r="AF75" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG75" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH75" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI75" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ75" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK75" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL75" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM75" s="6">
+        <v>2</v>
+      </c>
+      <c r="AN75" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO75" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP75" s="4">
         <v>58</v>
       </c>
@@ -14303,7 +14747,9 @@
       <c r="N90" s="6">
         <v>34</v>
       </c>
-      <c r="O90" s="6"/>
+      <c r="O90" s="6">
+        <v>23</v>
+      </c>
       <c r="P90" s="7">
         <v>4.320706060606061</v>
       </c>
@@ -14313,31 +14759,75 @@
       <c r="R90" s="8">
         <v>14.029708695652173</v>
       </c>
-      <c r="S90" s="8"/>
+      <c r="S90" s="8">
+        <v>7</v>
+      </c>
       <c r="T90" s="9">
         <v>0</v>
       </c>
-      <c r="U90" s="9"/>
-      <c r="V90" s="9"/>
-      <c r="W90" s="9"/>
-      <c r="X90" s="9"/>
-      <c r="Y90" s="9"/>
-      <c r="Z90" s="9"/>
-      <c r="AA90" s="9"/>
-      <c r="AB90" s="9"/>
-      <c r="AC90" s="9"/>
-      <c r="AD90" s="6"/>
-      <c r="AE90" s="6"/>
-      <c r="AF90" s="6"/>
-      <c r="AG90" s="6"/>
-      <c r="AH90" s="6"/>
-      <c r="AI90" s="6"/>
-      <c r="AJ90" s="6"/>
-      <c r="AK90" s="6"/>
-      <c r="AL90" s="6"/>
-      <c r="AM90" s="6"/>
-      <c r="AN90" s="9"/>
-      <c r="AO90" s="6"/>
+      <c r="U90" s="9">
+        <v>0.17391304347826086</v>
+      </c>
+      <c r="V90" s="9">
+        <v>0.043478260869565216</v>
+      </c>
+      <c r="W90" s="9">
+        <v>0</v>
+      </c>
+      <c r="X90" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y90" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z90" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA90" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB90" s="9">
+        <v>0.043478260869565216</v>
+      </c>
+      <c r="AC90" s="9">
+        <v>0.086956521739130432</v>
+      </c>
+      <c r="AD90" s="6">
+        <v>4</v>
+      </c>
+      <c r="AE90" s="6">
+        <v>4</v>
+      </c>
+      <c r="AF90" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG90" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH90" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI90" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ90" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK90" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL90" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM90" s="6">
+        <v>2</v>
+      </c>
+      <c r="AN90" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO90" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP90" s="4">
         <v>58</v>
       </c>
@@ -14571,35 +15061,81 @@
       <c r="N92" s="6">
         <v>34</v>
       </c>
-      <c r="O92" s="6"/>
+      <c r="O92" s="6">
+        <v>19</v>
+      </c>
       <c r="P92" s="7">
         <v>4.2378378378378381</v>
       </c>
       <c r="Q92" s="8"/>
       <c r="R92" s="8"/>
-      <c r="S92" s="8"/>
+      <c r="S92" s="8">
+        <v>8</v>
+      </c>
       <c r="T92" s="9"/>
-      <c r="U92" s="9"/>
-      <c r="V92" s="9"/>
-      <c r="W92" s="9"/>
-      <c r="X92" s="9"/>
-      <c r="Y92" s="9"/>
-      <c r="Z92" s="9"/>
-      <c r="AA92" s="9"/>
-      <c r="AB92" s="9"/>
-      <c r="AC92" s="9"/>
-      <c r="AD92" s="6"/>
-      <c r="AE92" s="6"/>
-      <c r="AF92" s="6"/>
-      <c r="AG92" s="6"/>
-      <c r="AH92" s="6"/>
-      <c r="AI92" s="6"/>
-      <c r="AJ92" s="6"/>
-      <c r="AK92" s="6"/>
-      <c r="AL92" s="6"/>
-      <c r="AM92" s="6"/>
-      <c r="AN92" s="9"/>
-      <c r="AO92" s="6"/>
+      <c r="U92" s="9">
+        <v>0.52631578947368418</v>
+      </c>
+      <c r="V92" s="9">
+        <v>0</v>
+      </c>
+      <c r="W92" s="9">
+        <v>0</v>
+      </c>
+      <c r="X92" s="9">
+        <v>0.052631578947368418</v>
+      </c>
+      <c r="Y92" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z92" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA92" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB92" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC92" s="9">
+        <v>0.52631578947368418</v>
+      </c>
+      <c r="AD92" s="6">
+        <v>11</v>
+      </c>
+      <c r="AE92" s="6">
+        <v>10</v>
+      </c>
+      <c r="AF92" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG92" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH92" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI92" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ92" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK92" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL92" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM92" s="6">
+        <v>10</v>
+      </c>
+      <c r="AN92" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO92" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP92" s="4">
         <v>58</v>
       </c>
@@ -17000,7 +17536,9 @@
       <c r="N109" s="6">
         <v>48</v>
       </c>
-      <c r="O109" s="6"/>
+      <c r="O109" s="6">
+        <v>7</v>
+      </c>
       <c r="P109" s="7">
         <v>4.240136734693877</v>
       </c>
@@ -17010,31 +17548,75 @@
       <c r="R109" s="8">
         <v>8.3023857142857143</v>
       </c>
-      <c r="S109" s="8"/>
+      <c r="S109" s="8">
+        <v>8</v>
+      </c>
       <c r="T109" s="9">
         <v>0.14285714285714285</v>
       </c>
-      <c r="U109" s="9"/>
-      <c r="V109" s="9"/>
-      <c r="W109" s="9"/>
-      <c r="X109" s="9"/>
-      <c r="Y109" s="9"/>
-      <c r="Z109" s="9"/>
-      <c r="AA109" s="9"/>
-      <c r="AB109" s="9"/>
-      <c r="AC109" s="9"/>
-      <c r="AD109" s="6"/>
-      <c r="AE109" s="6"/>
-      <c r="AF109" s="6"/>
-      <c r="AG109" s="6"/>
-      <c r="AH109" s="6"/>
-      <c r="AI109" s="6"/>
-      <c r="AJ109" s="6"/>
-      <c r="AK109" s="6"/>
-      <c r="AL109" s="6"/>
-      <c r="AM109" s="6"/>
-      <c r="AN109" s="9"/>
-      <c r="AO109" s="6"/>
+      <c r="U109" s="9">
+        <v>0.42857142857142855</v>
+      </c>
+      <c r="V109" s="9">
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="W109" s="9">
+        <v>0</v>
+      </c>
+      <c r="X109" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y109" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z109" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA109" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB109" s="9">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="AC109" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD109" s="6">
+        <v>3</v>
+      </c>
+      <c r="AE109" s="6">
+        <v>3</v>
+      </c>
+      <c r="AF109" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG109" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH109" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI109" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ109" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK109" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL109" s="6">
+        <v>2</v>
+      </c>
+      <c r="AM109" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN109" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO109" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP109" s="4">
         <v>58</v>
       </c>
@@ -18298,7 +18880,9 @@
       <c r="N119" s="6">
         <v>37</v>
       </c>
-      <c r="O119" s="6"/>
+      <c r="O119" s="6">
+        <v>15</v>
+      </c>
       <c r="P119" s="7">
         <v>2.5409918918918919</v>
       </c>
@@ -18308,31 +18892,75 @@
       <c r="R119" s="8">
         <v>5.2677800000000001</v>
       </c>
-      <c r="S119" s="8"/>
+      <c r="S119" s="8">
+        <v>7</v>
+      </c>
       <c r="T119" s="9">
         <v>0.80000000000000004</v>
       </c>
-      <c r="U119" s="9"/>
-      <c r="V119" s="9"/>
-      <c r="W119" s="9"/>
-      <c r="X119" s="9"/>
-      <c r="Y119" s="9"/>
-      <c r="Z119" s="9"/>
-      <c r="AA119" s="9"/>
-      <c r="AB119" s="9"/>
-      <c r="AC119" s="9"/>
-      <c r="AD119" s="6"/>
-      <c r="AE119" s="6"/>
-      <c r="AF119" s="6"/>
-      <c r="AG119" s="6"/>
-      <c r="AH119" s="6"/>
-      <c r="AI119" s="6"/>
-      <c r="AJ119" s="6"/>
-      <c r="AK119" s="6"/>
-      <c r="AL119" s="6"/>
-      <c r="AM119" s="6"/>
-      <c r="AN119" s="9"/>
-      <c r="AO119" s="6"/>
+      <c r="U119" s="9">
+        <v>0</v>
+      </c>
+      <c r="V119" s="9">
+        <v>0</v>
+      </c>
+      <c r="W119" s="9">
+        <v>0</v>
+      </c>
+      <c r="X119" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y119" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z119" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA119" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB119" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC119" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD119" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE119" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF119" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG119" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH119" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI119" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ119" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK119" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL119" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM119" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN119" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO119" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP119" s="4">
         <v>58</v>
       </c>
@@ -21735,7 +22363,9 @@
       <c r="N142" s="6">
         <v>61</v>
       </c>
-      <c r="O142" s="6"/>
+      <c r="O142" s="6">
+        <v>24</v>
+      </c>
       <c r="P142" s="7">
         <v>2.861945</v>
       </c>
@@ -21745,31 +22375,75 @@
       <c r="R142" s="8">
         <v>4.9469681818181819</v>
       </c>
-      <c r="S142" s="8"/>
+      <c r="S142" s="8">
+        <v>8.9000000000000004</v>
+      </c>
       <c r="T142" s="9">
         <v>0.5</v>
       </c>
-      <c r="U142" s="9"/>
-      <c r="V142" s="9"/>
-      <c r="W142" s="9"/>
-      <c r="X142" s="9"/>
-      <c r="Y142" s="9"/>
-      <c r="Z142" s="9"/>
-      <c r="AA142" s="9"/>
-      <c r="AB142" s="9"/>
-      <c r="AC142" s="9"/>
-      <c r="AD142" s="6"/>
-      <c r="AE142" s="6"/>
-      <c r="AF142" s="6"/>
-      <c r="AG142" s="6"/>
-      <c r="AH142" s="6"/>
-      <c r="AI142" s="6"/>
-      <c r="AJ142" s="6"/>
-      <c r="AK142" s="6"/>
-      <c r="AL142" s="6"/>
-      <c r="AM142" s="6"/>
-      <c r="AN142" s="9"/>
-      <c r="AO142" s="6"/>
+      <c r="U142" s="9">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="V142" s="9">
+        <v>0.083333333333333329</v>
+      </c>
+      <c r="W142" s="9">
+        <v>0</v>
+      </c>
+      <c r="X142" s="9">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="Y142" s="9">
+        <v>0.041666666666666664</v>
+      </c>
+      <c r="Z142" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA142" s="9">
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="AB142" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC142" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD142" s="6">
+        <v>12</v>
+      </c>
+      <c r="AE142" s="6">
+        <v>7</v>
+      </c>
+      <c r="AF142" s="6">
+        <v>2</v>
+      </c>
+      <c r="AG142" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH142" s="6">
+        <v>4</v>
+      </c>
+      <c r="AI142" s="6">
+        <v>1</v>
+      </c>
+      <c r="AJ142" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK142" s="6">
+        <v>5</v>
+      </c>
+      <c r="AL142" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM142" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN142" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO142" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP142" s="4">
         <v>58</v>
       </c>
@@ -22593,7 +23267,7 @@
         <v>19809</v>
       </c>
       <c r="B148" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C148" s="4">
         <v>51</v>
@@ -22623,35 +23297,93 @@
         <v>58</v>
       </c>
       <c r="L148" s="4"/>
-      <c r="M148" s="5"/>
-      <c r="N148" s="6"/>
-      <c r="O148" s="6"/>
-      <c r="P148" s="7"/>
-      <c r="Q148" s="8"/>
-      <c r="R148" s="8"/>
-      <c r="S148" s="8"/>
-      <c r="T148" s="9"/>
-      <c r="U148" s="9"/>
-      <c r="V148" s="9"/>
-      <c r="W148" s="9"/>
-      <c r="X148" s="9"/>
-      <c r="Y148" s="9"/>
-      <c r="Z148" s="9"/>
-      <c r="AA148" s="9"/>
-      <c r="AB148" s="9"/>
-      <c r="AC148" s="9"/>
-      <c r="AD148" s="6"/>
-      <c r="AE148" s="6"/>
-      <c r="AF148" s="6"/>
-      <c r="AG148" s="6"/>
-      <c r="AH148" s="6"/>
-      <c r="AI148" s="6"/>
-      <c r="AJ148" s="6"/>
-      <c r="AK148" s="6"/>
-      <c r="AL148" s="6"/>
-      <c r="AM148" s="6"/>
-      <c r="AN148" s="9"/>
-      <c r="AO148" s="6"/>
+      <c r="M148" s="5">
+        <v>5244.1400000000003</v>
+      </c>
+      <c r="N148" s="6">
+        <v>61</v>
+      </c>
+      <c r="O148" s="6">
+        <v>41</v>
+      </c>
+      <c r="P148" s="7">
+        <v>6.9279661016949152</v>
+      </c>
+      <c r="Q148" s="8">
+        <v>31.811382926829268</v>
+      </c>
+      <c r="R148" s="8">
+        <v>16.781300000000002</v>
+      </c>
+      <c r="S148" s="8">
+        <v>8</v>
+      </c>
+      <c r="T148" s="9">
+        <v>0.04878048780487805</v>
+      </c>
+      <c r="U148" s="9">
+        <v>0.073170731707317069</v>
+      </c>
+      <c r="V148" s="9">
+        <v>0.024390243902439025</v>
+      </c>
+      <c r="W148" s="9">
+        <v>0</v>
+      </c>
+      <c r="X148" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y148" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z148" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA148" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB148" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC148" s="9">
+        <v>0.04878048780487805</v>
+      </c>
+      <c r="AD148" s="6">
+        <v>3</v>
+      </c>
+      <c r="AE148" s="6">
+        <v>3</v>
+      </c>
+      <c r="AF148" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG148" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH148" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI148" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ148" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK148" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL148" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM148" s="6">
+        <v>2</v>
+      </c>
+      <c r="AN148" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO148" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP148" s="4">
         <v>58</v>
       </c>
@@ -23787,7 +24519,7 @@
         <v>19847</v>
       </c>
       <c r="B156" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C156" s="4">
         <v>51</v>
@@ -23817,18 +24549,30 @@
         <v>58</v>
       </c>
       <c r="L156" s="4"/>
-      <c r="M156" s="5"/>
-      <c r="N156" s="6"/>
+      <c r="M156" s="5">
+        <v>4394.9099999999999</v>
+      </c>
+      <c r="N156" s="6">
+        <v>45</v>
+      </c>
       <c r="O156" s="6">
         <v>34</v>
       </c>
-      <c r="P156" s="7"/>
-      <c r="Q156" s="8"/>
-      <c r="R156" s="8"/>
+      <c r="P156" s="7">
+        <v>8.5931818181818187</v>
+      </c>
+      <c r="Q156" s="8">
+        <v>19.138235294117649</v>
+      </c>
+      <c r="R156" s="8">
+        <v>3.9439393939393943</v>
+      </c>
       <c r="S156" s="8">
         <v>7</v>
       </c>
-      <c r="T156" s="9"/>
+      <c r="T156" s="9">
+        <v>0.23529411764705882</v>
+      </c>
       <c r="U156" s="9">
         <v>0.26470588235294118</v>
       </c>
@@ -24579,7 +25323,9 @@
       <c r="N162" s="6">
         <v>41</v>
       </c>
-      <c r="O162" s="6"/>
+      <c r="O162" s="6">
+        <v>26</v>
+      </c>
       <c r="P162" s="7">
         <v>8.7004175000000004</v>
       </c>
@@ -24589,31 +25335,75 @@
       <c r="R162" s="8">
         <v>7.2519230769230774</v>
       </c>
-      <c r="S162" s="8"/>
+      <c r="S162" s="8">
+        <v>8</v>
+      </c>
       <c r="T162" s="9">
         <v>0</v>
       </c>
-      <c r="U162" s="9"/>
-      <c r="V162" s="9"/>
-      <c r="W162" s="9"/>
-      <c r="X162" s="9"/>
-      <c r="Y162" s="9"/>
-      <c r="Z162" s="9"/>
-      <c r="AA162" s="9"/>
-      <c r="AB162" s="9"/>
-      <c r="AC162" s="9"/>
-      <c r="AD162" s="6"/>
-      <c r="AE162" s="6"/>
-      <c r="AF162" s="6"/>
-      <c r="AG162" s="6"/>
-      <c r="AH162" s="6"/>
-      <c r="AI162" s="6"/>
-      <c r="AJ162" s="6"/>
-      <c r="AK162" s="6"/>
-      <c r="AL162" s="6"/>
-      <c r="AM162" s="6"/>
-      <c r="AN162" s="9"/>
-      <c r="AO162" s="6"/>
+      <c r="U162" s="9">
+        <v>0.34615384615384615</v>
+      </c>
+      <c r="V162" s="9">
+        <v>0.038461538461538464</v>
+      </c>
+      <c r="W162" s="9">
+        <v>0</v>
+      </c>
+      <c r="X162" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y162" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z162" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA162" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB162" s="9">
+        <v>0.038461538461538464</v>
+      </c>
+      <c r="AC162" s="9">
+        <v>0.30769230769230771</v>
+      </c>
+      <c r="AD162" s="6">
+        <v>10</v>
+      </c>
+      <c r="AE162" s="6">
+        <v>9</v>
+      </c>
+      <c r="AF162" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG162" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH162" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI162" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ162" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK162" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL162" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM162" s="6">
+        <v>8</v>
+      </c>
+      <c r="AN162" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO162" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP162" s="4">
         <v>58</v>
       </c>
@@ -26514,7 +27304,9 @@
       <c r="N175" s="6">
         <v>34</v>
       </c>
-      <c r="O175" s="6"/>
+      <c r="O175" s="6">
+        <v>18</v>
+      </c>
       <c r="P175" s="7">
         <v>9.9716666666666658</v>
       </c>
@@ -26524,31 +27316,75 @@
       <c r="R175" s="8">
         <v>1.4435166666666666</v>
       </c>
-      <c r="S175" s="8"/>
+      <c r="S175" s="8">
+        <v>7</v>
+      </c>
       <c r="T175" s="9">
         <v>0.5</v>
       </c>
-      <c r="U175" s="9"/>
-      <c r="V175" s="9"/>
-      <c r="W175" s="9"/>
-      <c r="X175" s="9"/>
-      <c r="Y175" s="9"/>
-      <c r="Z175" s="9"/>
-      <c r="AA175" s="9"/>
-      <c r="AB175" s="9"/>
-      <c r="AC175" s="9"/>
-      <c r="AD175" s="6"/>
-      <c r="AE175" s="6"/>
-      <c r="AF175" s="6"/>
-      <c r="AG175" s="6"/>
-      <c r="AH175" s="6"/>
-      <c r="AI175" s="6"/>
-      <c r="AJ175" s="6"/>
-      <c r="AK175" s="6"/>
-      <c r="AL175" s="6"/>
-      <c r="AM175" s="6"/>
-      <c r="AN175" s="9"/>
-      <c r="AO175" s="6"/>
+      <c r="U175" s="9">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="V175" s="9">
+        <v>0.055555555555555552</v>
+      </c>
+      <c r="W175" s="9">
+        <v>0</v>
+      </c>
+      <c r="X175" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y175" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z175" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA175" s="9">
+        <v>0.055555555555555552</v>
+      </c>
+      <c r="AB175" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC175" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD175" s="6">
+        <v>2</v>
+      </c>
+      <c r="AE175" s="6">
+        <v>2</v>
+      </c>
+      <c r="AF175" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG175" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH175" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI175" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ175" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK175" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL175" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM175" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN175" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO175" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP175" s="4">
         <v>58</v>
       </c>
@@ -27358,7 +28194,9 @@
       <c r="N181" s="6">
         <v>28</v>
       </c>
-      <c r="O181" s="6"/>
+      <c r="O181" s="6">
+        <v>21</v>
+      </c>
       <c r="P181" s="7">
         <v>3.0942517241379308</v>
       </c>
@@ -27368,31 +28206,75 @@
       <c r="R181" s="8">
         <v>1.1694500000000001</v>
       </c>
-      <c r="S181" s="8"/>
+      <c r="S181" s="8">
+        <v>8</v>
+      </c>
       <c r="T181" s="9">
         <v>0.95238095238095233</v>
       </c>
-      <c r="U181" s="9"/>
-      <c r="V181" s="9"/>
-      <c r="W181" s="9"/>
-      <c r="X181" s="9"/>
-      <c r="Y181" s="9"/>
-      <c r="Z181" s="9"/>
-      <c r="AA181" s="9"/>
-      <c r="AB181" s="9"/>
-      <c r="AC181" s="9"/>
-      <c r="AD181" s="6"/>
-      <c r="AE181" s="6"/>
-      <c r="AF181" s="6"/>
-      <c r="AG181" s="6"/>
-      <c r="AH181" s="6"/>
-      <c r="AI181" s="6"/>
-      <c r="AJ181" s="6"/>
-      <c r="AK181" s="6"/>
-      <c r="AL181" s="6"/>
-      <c r="AM181" s="6"/>
-      <c r="AN181" s="9"/>
-      <c r="AO181" s="6"/>
+      <c r="U181" s="9">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="V181" s="9">
+        <v>0</v>
+      </c>
+      <c r="W181" s="9">
+        <v>0</v>
+      </c>
+      <c r="X181" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y181" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z181" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA181" s="9">
+        <v>0.76190476190476186</v>
+      </c>
+      <c r="AB181" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC181" s="9">
+        <v>0.19047619047619047</v>
+      </c>
+      <c r="AD181" s="6">
+        <v>20</v>
+      </c>
+      <c r="AE181" s="6">
+        <v>18</v>
+      </c>
+      <c r="AF181" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG181" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH181" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI181" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ181" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK181" s="6">
+        <v>16</v>
+      </c>
+      <c r="AL181" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM181" s="6">
+        <v>4</v>
+      </c>
+      <c r="AN181" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO181" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP181" s="4">
         <v>58</v>
       </c>
@@ -28196,7 +29078,9 @@
       <c r="N187" s="6">
         <v>18</v>
       </c>
-      <c r="O187" s="6"/>
+      <c r="O187" s="6">
+        <v>13</v>
+      </c>
       <c r="P187" s="7">
         <v>9.9583333333333339</v>
       </c>
@@ -28206,31 +29090,75 @@
       <c r="R187" s="8">
         <v>14.256407692307693</v>
       </c>
-      <c r="S187" s="8"/>
+      <c r="S187" s="8">
+        <v>7</v>
+      </c>
       <c r="T187" s="9">
         <v>0</v>
       </c>
-      <c r="U187" s="9"/>
-      <c r="V187" s="9"/>
-      <c r="W187" s="9"/>
-      <c r="X187" s="9"/>
-      <c r="Y187" s="9"/>
-      <c r="Z187" s="9"/>
-      <c r="AA187" s="9"/>
-      <c r="AB187" s="9"/>
-      <c r="AC187" s="9"/>
-      <c r="AD187" s="6"/>
-      <c r="AE187" s="6"/>
-      <c r="AF187" s="6"/>
-      <c r="AG187" s="6"/>
-      <c r="AH187" s="6"/>
-      <c r="AI187" s="6"/>
-      <c r="AJ187" s="6"/>
-      <c r="AK187" s="6"/>
-      <c r="AL187" s="6"/>
-      <c r="AM187" s="6"/>
-      <c r="AN187" s="9"/>
-      <c r="AO187" s="6"/>
+      <c r="U187" s="9">
+        <v>0.15384615384615385</v>
+      </c>
+      <c r="V187" s="9">
+        <v>0</v>
+      </c>
+      <c r="W187" s="9">
+        <v>0</v>
+      </c>
+      <c r="X187" s="9">
+        <v>0.15384615384615385</v>
+      </c>
+      <c r="Y187" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z187" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA187" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB187" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC187" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD187" s="6">
+        <v>2</v>
+      </c>
+      <c r="AE187" s="6">
+        <v>2</v>
+      </c>
+      <c r="AF187" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG187" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH187" s="6">
+        <v>2</v>
+      </c>
+      <c r="AI187" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ187" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK187" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL187" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM187" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN187" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO187" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP187" s="4">
         <v>58</v>
       </c>
@@ -28621,7 +29549,9 @@
       <c r="N190" s="6">
         <v>40</v>
       </c>
-      <c r="O190" s="6"/>
+      <c r="O190" s="6">
+        <v>18</v>
+      </c>
       <c r="P190" s="7">
         <v>4.2000000000000002</v>
       </c>
@@ -28631,31 +29561,75 @@
       <c r="R190" s="8">
         <v>3.7901941176470588</v>
       </c>
-      <c r="S190" s="8"/>
+      <c r="S190" s="8">
+        <v>7</v>
+      </c>
       <c r="T190" s="9">
         <v>0.55555555555555558</v>
       </c>
-      <c r="U190" s="9"/>
-      <c r="V190" s="9"/>
-      <c r="W190" s="9"/>
-      <c r="X190" s="9"/>
-      <c r="Y190" s="9"/>
-      <c r="Z190" s="9"/>
-      <c r="AA190" s="9"/>
-      <c r="AB190" s="9"/>
-      <c r="AC190" s="9"/>
-      <c r="AD190" s="6"/>
-      <c r="AE190" s="6"/>
-      <c r="AF190" s="6"/>
-      <c r="AG190" s="6"/>
-      <c r="AH190" s="6"/>
-      <c r="AI190" s="6"/>
-      <c r="AJ190" s="6"/>
-      <c r="AK190" s="6"/>
-      <c r="AL190" s="6"/>
-      <c r="AM190" s="6"/>
-      <c r="AN190" s="9"/>
-      <c r="AO190" s="6"/>
+      <c r="U190" s="9">
+        <v>0.055555555555555552</v>
+      </c>
+      <c r="V190" s="9">
+        <v>0</v>
+      </c>
+      <c r="W190" s="9">
+        <v>0</v>
+      </c>
+      <c r="X190" s="9">
+        <v>0.055555555555555552</v>
+      </c>
+      <c r="Y190" s="9">
+        <v>0.055555555555555552</v>
+      </c>
+      <c r="Z190" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA190" s="9">
+        <v>0.055555555555555552</v>
+      </c>
+      <c r="AB190" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC190" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD190" s="6">
+        <v>3</v>
+      </c>
+      <c r="AE190" s="6">
+        <v>1</v>
+      </c>
+      <c r="AF190" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG190" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH190" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI190" s="6">
+        <v>1</v>
+      </c>
+      <c r="AJ190" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK190" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL190" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM190" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN190" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO190" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP190" s="4">
         <v>58</v>
       </c>
@@ -29421,7 +30395,7 @@
         <v>19945</v>
       </c>
       <c r="B196" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C196" s="4">
         <v>51</v>
@@ -29451,35 +30425,93 @@
         <v>58</v>
       </c>
       <c r="L196" s="4"/>
-      <c r="M196" s="5"/>
-      <c r="N196" s="6"/>
-      <c r="O196" s="6"/>
-      <c r="P196" s="7"/>
-      <c r="Q196" s="8"/>
-      <c r="R196" s="8"/>
-      <c r="S196" s="8"/>
-      <c r="T196" s="9"/>
-      <c r="U196" s="9"/>
-      <c r="V196" s="9"/>
-      <c r="W196" s="9"/>
-      <c r="X196" s="9"/>
-      <c r="Y196" s="9"/>
-      <c r="Z196" s="9"/>
-      <c r="AA196" s="9"/>
-      <c r="AB196" s="9"/>
-      <c r="AC196" s="9"/>
-      <c r="AD196" s="6"/>
-      <c r="AE196" s="6"/>
-      <c r="AF196" s="6"/>
-      <c r="AG196" s="6"/>
-      <c r="AH196" s="6"/>
-      <c r="AI196" s="6"/>
-      <c r="AJ196" s="6"/>
-      <c r="AK196" s="6"/>
-      <c r="AL196" s="6"/>
-      <c r="AM196" s="6"/>
-      <c r="AN196" s="9"/>
-      <c r="AO196" s="6"/>
+      <c r="M196" s="5">
+        <v>2333.75</v>
+      </c>
+      <c r="N196" s="6">
+        <v>29</v>
+      </c>
+      <c r="O196" s="6">
+        <v>3</v>
+      </c>
+      <c r="P196" s="7">
+        <v>7.4666652173913048</v>
+      </c>
+      <c r="Q196" s="8">
+        <v>15.6</v>
+      </c>
+      <c r="R196" s="8">
+        <v>1.2749999999999999</v>
+      </c>
+      <c r="S196" s="8">
+        <v>7</v>
+      </c>
+      <c r="T196" s="9">
+        <v>0</v>
+      </c>
+      <c r="U196" s="9">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="V196" s="9">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="W196" s="9">
+        <v>0</v>
+      </c>
+      <c r="X196" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y196" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z196" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA196" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB196" s="9">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="AC196" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD196" s="6">
+        <v>2</v>
+      </c>
+      <c r="AE196" s="6">
+        <v>1</v>
+      </c>
+      <c r="AF196" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG196" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH196" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI196" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ196" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK196" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL196" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM196" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN196" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO196" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP196" s="4">
         <v>58</v>
       </c>
@@ -30027,7 +31059,9 @@
       <c r="N200" s="6">
         <v>14</v>
       </c>
-      <c r="O200" s="6"/>
+      <c r="O200" s="6">
+        <v>6</v>
+      </c>
       <c r="P200" s="7">
         <v>5.148715384615385</v>
       </c>
@@ -30037,31 +31071,75 @@
       <c r="R200" s="8">
         <v>2.3722166666666666</v>
       </c>
-      <c r="S200" s="8"/>
+      <c r="S200" s="8">
+        <v>7</v>
+      </c>
       <c r="T200" s="9">
         <v>0.66666666666666663</v>
       </c>
-      <c r="U200" s="9"/>
-      <c r="V200" s="9"/>
-      <c r="W200" s="9"/>
-      <c r="X200" s="9"/>
-      <c r="Y200" s="9"/>
-      <c r="Z200" s="9"/>
-      <c r="AA200" s="9"/>
-      <c r="AB200" s="9"/>
-      <c r="AC200" s="9"/>
-      <c r="AD200" s="6"/>
-      <c r="AE200" s="6"/>
-      <c r="AF200" s="6"/>
-      <c r="AG200" s="6"/>
-      <c r="AH200" s="6"/>
-      <c r="AI200" s="6"/>
-      <c r="AJ200" s="6"/>
-      <c r="AK200" s="6"/>
-      <c r="AL200" s="6"/>
-      <c r="AM200" s="6"/>
-      <c r="AN200" s="9"/>
-      <c r="AO200" s="6"/>
+      <c r="U200" s="9">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="V200" s="9">
+        <v>0</v>
+      </c>
+      <c r="W200" s="9">
+        <v>0</v>
+      </c>
+      <c r="X200" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y200" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z200" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA200" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB200" s="9">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="AC200" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD200" s="6">
+        <v>2</v>
+      </c>
+      <c r="AE200" s="6">
+        <v>2</v>
+      </c>
+      <c r="AF200" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG200" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH200" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI200" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ200" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK200" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL200" s="6">
+        <v>2</v>
+      </c>
+      <c r="AM200" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN200" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO200" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP200" s="4">
         <v>58</v>
       </c>
@@ -30964,7 +32042,9 @@
       <c r="N207" s="6">
         <v>27</v>
       </c>
-      <c r="O207" s="6"/>
+      <c r="O207" s="6">
+        <v>11</v>
+      </c>
       <c r="P207" s="7">
         <v>7.7791678571428573</v>
       </c>
@@ -30974,31 +32054,75 @@
       <c r="R207" s="8">
         <v>7.8816699999999997</v>
       </c>
-      <c r="S207" s="8"/>
+      <c r="S207" s="8">
+        <v>7</v>
+      </c>
       <c r="T207" s="9">
         <v>0.18181818181818182</v>
       </c>
-      <c r="U207" s="9"/>
-      <c r="V207" s="9"/>
-      <c r="W207" s="9"/>
-      <c r="X207" s="9"/>
-      <c r="Y207" s="9"/>
-      <c r="Z207" s="9"/>
-      <c r="AA207" s="9"/>
-      <c r="AB207" s="9"/>
-      <c r="AC207" s="9"/>
-      <c r="AD207" s="6"/>
-      <c r="AE207" s="6"/>
-      <c r="AF207" s="6"/>
-      <c r="AG207" s="6"/>
-      <c r="AH207" s="6"/>
-      <c r="AI207" s="6"/>
-      <c r="AJ207" s="6"/>
-      <c r="AK207" s="6"/>
-      <c r="AL207" s="6"/>
-      <c r="AM207" s="6"/>
-      <c r="AN207" s="9"/>
-      <c r="AO207" s="6"/>
+      <c r="U207" s="9">
+        <v>0.18181818181818182</v>
+      </c>
+      <c r="V207" s="9">
+        <v>0</v>
+      </c>
+      <c r="W207" s="9">
+        <v>0</v>
+      </c>
+      <c r="X207" s="9">
+        <v>0.090909090909090912</v>
+      </c>
+      <c r="Y207" s="9">
+        <v>0.090909090909090912</v>
+      </c>
+      <c r="Z207" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA207" s="9">
+        <v>0.090909090909090912</v>
+      </c>
+      <c r="AB207" s="9">
+        <v>0.090909090909090912</v>
+      </c>
+      <c r="AC207" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD207" s="6">
+        <v>4</v>
+      </c>
+      <c r="AE207" s="6">
+        <v>2</v>
+      </c>
+      <c r="AF207" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG207" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH207" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI207" s="6">
+        <v>1</v>
+      </c>
+      <c r="AJ207" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK207" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL207" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM207" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN207" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO207" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP207" s="4">
         <v>58</v>
       </c>
@@ -32039,10 +33163,10 @@
         <v>335</v>
       </c>
       <c t="s" r="AN216" s="11">
-        <v>319</v>
+        <v>336</v>
       </c>
       <c t="s" r="AO216" s="11">
-        <v>311</v>
+        <v>337</v>
       </c>
       <c r="AP216" s="12"/>
       <c t="s" r="AQ216" s="12">
@@ -32059,10 +33183,10 @@
         <v>59</v>
       </c>
       <c t="s" r="AX216" s="11">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c t="s" r="AY216" s="11">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="AZ216" s="12"/>
       <c r="BA216" s="12"/>

--- a/novo projeto/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-17).xlsx
+++ b/novo projeto/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-17).xlsx
@@ -935,34 +935,34 @@
     <t>214</t>
   </si>
   <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>R$ 4.502,58</t>
-  </si>
-  <si>
-    <t>49.2</t>
-  </si>
-  <si>
-    <t>30.9</t>
-  </si>
-  <si>
-    <t>4.86</t>
-  </si>
-  <si>
-    <t>18.2</t>
-  </si>
-  <si>
-    <t>6.9</t>
-  </si>
-  <si>
-    <t>6.0</t>
-  </si>
-  <si>
-    <t>44.5%</t>
-  </si>
-  <si>
-    <t>19.9%</t>
+    <t>30</t>
+  </si>
+  <si>
+    <t>R$ 4.492,38</t>
+  </si>
+  <si>
+    <t>49.1</t>
+  </si>
+  <si>
+    <t>30.8</t>
+  </si>
+  <si>
+    <t>4.88</t>
+  </si>
+  <si>
+    <t>18.3</t>
+  </si>
+  <si>
+    <t>7.0</t>
+  </si>
+  <si>
+    <t>6.1</t>
+  </si>
+  <si>
+    <t>44.0%</t>
+  </si>
+  <si>
+    <t>19.7%</t>
   </si>
   <si>
     <t>1.9%</t>
@@ -983,25 +983,25 @@
     <t>7.7%</t>
   </si>
   <si>
-    <t>2.9%</t>
-  </si>
-  <si>
-    <t>4.7%</t>
-  </si>
-  <si>
-    <t>1361.0</t>
-  </si>
-  <si>
-    <t>1093.0</t>
-  </si>
-  <si>
-    <t>106.0</t>
-  </si>
-  <si>
-    <t>29.0</t>
-  </si>
-  <si>
-    <t>286.0</t>
+    <t>2.8%</t>
+  </si>
+  <si>
+    <t>4.6%</t>
+  </si>
+  <si>
+    <t>1369.0</t>
+  </si>
+  <si>
+    <t>1100.0</t>
+  </si>
+  <si>
+    <t>108.0</t>
+  </si>
+  <si>
+    <t>30.0</t>
+  </si>
+  <si>
+    <t>289.0</t>
   </si>
   <si>
     <t>84.0</t>
@@ -1010,10 +1010,10 @@
     <t>14.0</t>
   </si>
   <si>
-    <t>426.0</t>
-  </si>
-  <si>
-    <t>157.0</t>
+    <t>428.0</t>
+  </si>
+  <si>
+    <t>158.0</t>
   </si>
   <si>
     <t>256.0</t>
@@ -10097,33 +10097,79 @@
       <c r="L58" s="4"/>
       <c r="M58" s="5"/>
       <c r="N58" s="6"/>
-      <c r="O58" s="6"/>
+      <c r="O58" s="6">
+        <v>58</v>
+      </c>
       <c r="P58" s="7"/>
       <c r="Q58" s="8"/>
       <c r="R58" s="8"/>
-      <c r="S58" s="8"/>
+      <c r="S58" s="8">
+        <v>7</v>
+      </c>
       <c r="T58" s="9"/>
-      <c r="U58" s="9"/>
-      <c r="V58" s="9"/>
-      <c r="W58" s="9"/>
-      <c r="X58" s="9"/>
-      <c r="Y58" s="9"/>
-      <c r="Z58" s="9"/>
-      <c r="AA58" s="9"/>
-      <c r="AB58" s="9"/>
-      <c r="AC58" s="9"/>
-      <c r="AD58" s="6"/>
-      <c r="AE58" s="6"/>
-      <c r="AF58" s="6"/>
-      <c r="AG58" s="6"/>
-      <c r="AH58" s="6"/>
-      <c r="AI58" s="6"/>
-      <c r="AJ58" s="6"/>
-      <c r="AK58" s="6"/>
-      <c r="AL58" s="6"/>
-      <c r="AM58" s="6"/>
-      <c r="AN58" s="9"/>
-      <c r="AO58" s="6"/>
+      <c r="U58" s="9">
+        <v>0.051724137931034482</v>
+      </c>
+      <c r="V58" s="9">
+        <v>0.017241379310344827</v>
+      </c>
+      <c r="W58" s="9">
+        <v>0</v>
+      </c>
+      <c r="X58" s="9">
+        <v>0.034482758620689655</v>
+      </c>
+      <c r="Y58" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z58" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA58" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB58" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC58" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD58" s="6">
+        <v>3</v>
+      </c>
+      <c r="AE58" s="6">
+        <v>3</v>
+      </c>
+      <c r="AF58" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH58" s="6">
+        <v>2</v>
+      </c>
+      <c r="AI58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN58" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO58" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP58" s="4">
         <v>58</v>
       </c>
@@ -16521,7 +16567,7 @@
         <v>19719</v>
       </c>
       <c r="B102" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C102" s="4">
         <v>51</v>
@@ -16551,35 +16597,93 @@
         <v>58</v>
       </c>
       <c r="L102" s="4"/>
-      <c r="M102" s="5"/>
-      <c r="N102" s="6"/>
-      <c r="O102" s="6"/>
-      <c r="P102" s="7"/>
-      <c r="Q102" s="8"/>
-      <c r="R102" s="8"/>
-      <c r="S102" s="8"/>
-      <c r="T102" s="9"/>
-      <c r="U102" s="9"/>
-      <c r="V102" s="9"/>
-      <c r="W102" s="9"/>
-      <c r="X102" s="9"/>
-      <c r="Y102" s="9"/>
-      <c r="Z102" s="9"/>
-      <c r="AA102" s="9"/>
-      <c r="AB102" s="9"/>
-      <c r="AC102" s="9"/>
-      <c r="AD102" s="6"/>
-      <c r="AE102" s="6"/>
-      <c r="AF102" s="6"/>
-      <c r="AG102" s="6"/>
-      <c r="AH102" s="6"/>
-      <c r="AI102" s="6"/>
-      <c r="AJ102" s="6"/>
-      <c r="AK102" s="6"/>
-      <c r="AL102" s="6"/>
-      <c r="AM102" s="6"/>
-      <c r="AN102" s="9"/>
-      <c r="AO102" s="6"/>
+      <c r="M102" s="5">
+        <v>3242.4099999999999</v>
+      </c>
+      <c r="N102" s="6">
+        <v>31</v>
+      </c>
+      <c r="O102" s="6">
+        <v>15</v>
+      </c>
+      <c r="P102" s="7">
+        <v>9.1655566666666672</v>
+      </c>
+      <c r="Q102" s="8">
+        <v>37.997779999999999</v>
+      </c>
+      <c r="R102" s="8">
+        <v>25.173807142857139</v>
+      </c>
+      <c r="S102" s="8">
+        <v>7</v>
+      </c>
+      <c r="T102" s="9">
+        <v>0.20000000000000001</v>
+      </c>
+      <c r="U102" s="9">
+        <v>0.26666666666666666</v>
+      </c>
+      <c r="V102" s="9">
+        <v>0.066666666666666666</v>
+      </c>
+      <c r="W102" s="9">
+        <v>0.066666666666000005</v>
+      </c>
+      <c r="X102" s="9">
+        <v>0.066666666666666666</v>
+      </c>
+      <c r="Y102" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z102" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA102" s="9">
+        <v>0.13333333333333333</v>
+      </c>
+      <c r="AB102" s="9">
+        <v>0.066666666666666666</v>
+      </c>
+      <c r="AC102" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD102" s="6">
+        <v>5</v>
+      </c>
+      <c r="AE102" s="6">
+        <v>4</v>
+      </c>
+      <c r="AF102" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG102" s="6">
+        <v>1</v>
+      </c>
+      <c r="AH102" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI102" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ102" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK102" s="6">
+        <v>2</v>
+      </c>
+      <c r="AL102" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM102" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN102" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO102" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP102" s="4">
         <v>58</v>
       </c>
@@ -17792,7 +17896,9 @@
       <c r="N111" s="6">
         <v>11</v>
       </c>
-      <c r="O111" s="6"/>
+      <c r="O111" s="6">
+        <v>11</v>
+      </c>
       <c r="P111" s="7">
         <v>4.4333333333333336</v>
       </c>
@@ -17802,31 +17908,75 @@
       <c r="R111" s="8">
         <v>1.871209090909091</v>
       </c>
-      <c r="S111" s="8"/>
+      <c r="S111" s="8">
+        <v>7</v>
+      </c>
       <c r="T111" s="9">
         <v>0.63636363636363635</v>
       </c>
-      <c r="U111" s="9"/>
-      <c r="V111" s="9"/>
-      <c r="W111" s="9"/>
-      <c r="X111" s="9"/>
-      <c r="Y111" s="9"/>
-      <c r="Z111" s="9"/>
-      <c r="AA111" s="9"/>
-      <c r="AB111" s="9"/>
-      <c r="AC111" s="9"/>
-      <c r="AD111" s="6"/>
-      <c r="AE111" s="6"/>
-      <c r="AF111" s="6"/>
-      <c r="AG111" s="6"/>
-      <c r="AH111" s="6"/>
-      <c r="AI111" s="6"/>
-      <c r="AJ111" s="6"/>
-      <c r="AK111" s="6"/>
-      <c r="AL111" s="6"/>
-      <c r="AM111" s="6"/>
-      <c r="AN111" s="9"/>
-      <c r="AO111" s="6"/>
+      <c r="U111" s="9">
+        <v>0</v>
+      </c>
+      <c r="V111" s="9">
+        <v>0</v>
+      </c>
+      <c r="W111" s="9">
+        <v>0</v>
+      </c>
+      <c r="X111" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y111" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z111" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA111" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB111" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC111" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD111" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE111" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF111" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG111" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH111" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI111" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ111" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK111" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL111" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM111" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN111" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO111" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP111" s="4">
         <v>58</v>
       </c>
@@ -30296,7 +30446,7 @@
         <v>19944</v>
       </c>
       <c r="B195" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C195" s="4">
         <v>51</v>
@@ -30326,14 +30476,26 @@
         <v>58</v>
       </c>
       <c r="L195" s="4"/>
-      <c r="M195" s="5"/>
-      <c r="N195" s="6"/>
+      <c r="M195" s="5">
+        <v>3884.8899999999999</v>
+      </c>
+      <c r="N195" s="6">
+        <v>46</v>
+      </c>
       <c r="O195" s="6"/>
-      <c r="P195" s="7"/>
-      <c r="Q195" s="8"/>
-      <c r="R195" s="8"/>
+      <c r="P195" s="7">
+        <v>4.7570377777777777</v>
+      </c>
+      <c r="Q195" s="8">
+        <v>17.661538461538463</v>
+      </c>
+      <c r="R195" s="8">
+        <v>6.7153320000000001</v>
+      </c>
       <c r="S195" s="8"/>
-      <c r="T195" s="9"/>
+      <c r="T195" s="9">
+        <v>0.30769230769230771</v>
+      </c>
       <c r="U195" s="9"/>
       <c r="V195" s="9"/>
       <c r="W195" s="9"/>

--- a/novo projeto/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-17).xlsx
+++ b/novo projeto/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-17).xlsx
@@ -935,40 +935,40 @@
     <t>214</t>
   </si>
   <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>R$ 4.492,38</t>
-  </si>
-  <si>
-    <t>49.1</t>
-  </si>
-  <si>
-    <t>30.8</t>
-  </si>
-  <si>
-    <t>4.88</t>
+    <t>28</t>
+  </si>
+  <si>
+    <t>R$ 4.507,86</t>
+  </si>
+  <si>
+    <t>49.4</t>
+  </si>
+  <si>
+    <t>30.9</t>
+  </si>
+  <si>
+    <t>4.86</t>
   </si>
   <si>
     <t>18.3</t>
   </si>
   <si>
-    <t>7.0</t>
-  </si>
-  <si>
-    <t>6.1</t>
-  </si>
-  <si>
-    <t>44.0%</t>
-  </si>
-  <si>
-    <t>19.7%</t>
+    <t>7.1</t>
+  </si>
+  <si>
+    <t>6.2</t>
+  </si>
+  <si>
+    <t>43.7%</t>
+  </si>
+  <si>
+    <t>19.8%</t>
   </si>
   <si>
     <t>1.9%</t>
   </si>
   <si>
-    <t>0.5%</t>
+    <t>0.6%</t>
   </si>
   <si>
     <t>5.2%</t>
@@ -977,31 +977,31 @@
     <t>1.5%</t>
   </si>
   <si>
-    <t>0.3%</t>
-  </si>
-  <si>
-    <t>7.7%</t>
+    <t>0.2%</t>
+  </si>
+  <si>
+    <t>7.8%</t>
   </si>
   <si>
     <t>2.8%</t>
   </si>
   <si>
-    <t>4.6%</t>
-  </si>
-  <si>
-    <t>1369.0</t>
-  </si>
-  <si>
-    <t>1100.0</t>
-  </si>
-  <si>
-    <t>108.0</t>
-  </si>
-  <si>
-    <t>30.0</t>
-  </si>
-  <si>
-    <t>289.0</t>
+    <t>4.5%</t>
+  </si>
+  <si>
+    <t>1398.0</t>
+  </si>
+  <si>
+    <t>1129.0</t>
+  </si>
+  <si>
+    <t>109.0</t>
+  </si>
+  <si>
+    <t>32.0</t>
+  </si>
+  <si>
+    <t>297.0</t>
   </si>
   <si>
     <t>84.0</t>
@@ -1010,19 +1010,13 @@
     <t>14.0</t>
   </si>
   <si>
-    <t>428.0</t>
-  </si>
-  <si>
-    <t>158.0</t>
+    <t>446.0</t>
+  </si>
+  <si>
+    <t>160.0</t>
   </si>
   <si>
     <t>256.0</t>
-  </si>
-  <si>
-    <t>0.6%</t>
-  </si>
-  <si>
-    <t>32.0</t>
   </si>
   <si>
     <t>1</t>
@@ -3278,7 +3272,9 @@
       <c r="N13" s="6">
         <v>66</v>
       </c>
-      <c r="O13" s="6"/>
+      <c r="O13" s="6">
+        <v>47</v>
+      </c>
       <c r="P13" s="7">
         <v>4.879040909090909</v>
       </c>
@@ -3288,31 +3284,75 @@
       <c r="R13" s="8">
         <v>8.8581553191489366</v>
       </c>
-      <c r="S13" s="8"/>
+      <c r="S13" s="8">
+        <v>7</v>
+      </c>
       <c r="T13" s="9">
         <v>0.21276595744680851</v>
       </c>
-      <c r="U13" s="9"/>
-      <c r="V13" s="9"/>
-      <c r="W13" s="9"/>
-      <c r="X13" s="9"/>
-      <c r="Y13" s="9"/>
-      <c r="Z13" s="9"/>
-      <c r="AA13" s="9"/>
-      <c r="AB13" s="9"/>
-      <c r="AC13" s="9"/>
-      <c r="AD13" s="6"/>
-      <c r="AE13" s="6"/>
-      <c r="AF13" s="6"/>
-      <c r="AG13" s="6"/>
-      <c r="AH13" s="6"/>
-      <c r="AI13" s="6"/>
-      <c r="AJ13" s="6"/>
-      <c r="AK13" s="6"/>
-      <c r="AL13" s="6"/>
-      <c r="AM13" s="6"/>
-      <c r="AN13" s="9"/>
-      <c r="AO13" s="6"/>
+      <c r="U13" s="9">
+        <v>0.1276595744680851</v>
+      </c>
+      <c r="V13" s="9">
+        <v>0.021276595744680851</v>
+      </c>
+      <c r="W13" s="9">
+        <v>0</v>
+      </c>
+      <c r="X13" s="9">
+        <v>0.10638297872340426</v>
+      </c>
+      <c r="Y13" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB13" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC13" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD13" s="6">
+        <v>6</v>
+      </c>
+      <c r="AE13" s="6">
+        <v>6</v>
+      </c>
+      <c r="AF13" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG13" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="6">
+        <v>5</v>
+      </c>
+      <c r="AI13" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ13" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK13" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL13" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM13" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN13" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO13" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP13" s="4">
         <v>58</v>
       </c>
@@ -10065,7 +10105,7 @@
         <v>19618</v>
       </c>
       <c r="B58" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C58" s="4">
         <v>51</v>
@@ -10095,26 +10135,38 @@
         <v>58</v>
       </c>
       <c r="L58" s="4"/>
-      <c r="M58" s="5"/>
-      <c r="N58" s="6"/>
+      <c r="M58" s="5">
+        <v>5793.6899999999996</v>
+      </c>
+      <c r="N58" s="6">
+        <v>72</v>
+      </c>
       <c r="O58" s="6">
         <v>58</v>
       </c>
-      <c r="P58" s="7"/>
-      <c r="Q58" s="8"/>
-      <c r="R58" s="8"/>
+      <c r="P58" s="7">
+        <v>2.7065732394366195</v>
+      </c>
+      <c r="Q58" s="8">
+        <v>28.170689655172417</v>
+      </c>
+      <c r="R58" s="8">
+        <v>18.283332758620688</v>
+      </c>
       <c r="S58" s="8">
         <v>7</v>
       </c>
-      <c r="T58" s="9"/>
+      <c r="T58" s="9">
+        <v>0.1206896551724138</v>
+      </c>
       <c r="U58" s="9">
-        <v>0.051724137931034482</v>
+        <v>0.086206896551724144</v>
       </c>
       <c r="V58" s="9">
         <v>0.017241379310344827</v>
       </c>
       <c r="W58" s="9">
-        <v>0</v>
+        <v>0.034482758619999998</v>
       </c>
       <c r="X58" s="9">
         <v>0.034482758620689655</v>
@@ -10138,13 +10190,13 @@
         <v>3</v>
       </c>
       <c r="AE58" s="6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AF58" s="6">
         <v>1</v>
       </c>
       <c r="AG58" s="6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH58" s="6">
         <v>2</v>
@@ -12745,7 +12797,7 @@
         <v>19661</v>
       </c>
       <c r="B76" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C76" s="4">
         <v>51</v>
@@ -12773,35 +12825,93 @@
         <v>58</v>
       </c>
       <c r="L76" s="4"/>
-      <c r="M76" s="5"/>
-      <c r="N76" s="6"/>
-      <c r="O76" s="6"/>
-      <c r="P76" s="7"/>
-      <c r="Q76" s="8"/>
-      <c r="R76" s="8"/>
-      <c r="S76" s="8"/>
-      <c r="T76" s="9"/>
-      <c r="U76" s="9"/>
-      <c r="V76" s="9"/>
-      <c r="W76" s="9"/>
-      <c r="X76" s="9"/>
-      <c r="Y76" s="9"/>
-      <c r="Z76" s="9"/>
-      <c r="AA76" s="9"/>
-      <c r="AB76" s="9"/>
-      <c r="AC76" s="9"/>
-      <c r="AD76" s="6"/>
-      <c r="AE76" s="6"/>
-      <c r="AF76" s="6"/>
-      <c r="AG76" s="6"/>
-      <c r="AH76" s="6"/>
-      <c r="AI76" s="6"/>
-      <c r="AJ76" s="6"/>
-      <c r="AK76" s="6"/>
-      <c r="AL76" s="6"/>
-      <c r="AM76" s="6"/>
-      <c r="AN76" s="9"/>
-      <c r="AO76" s="6"/>
+      <c r="M76" s="5">
+        <v>6071.2399999999998</v>
+      </c>
+      <c r="N76" s="6">
+        <v>72</v>
+      </c>
+      <c r="O76" s="6">
+        <v>33</v>
+      </c>
+      <c r="P76" s="7">
+        <v>2.6763888888888889</v>
+      </c>
+      <c r="Q76" s="8">
+        <v>12.719696969696969</v>
+      </c>
+      <c r="R76" s="8">
+        <v>3.3516649999999997</v>
+      </c>
+      <c r="S76" s="8">
+        <v>9</v>
+      </c>
+      <c r="T76" s="9">
+        <v>0.72727272727272729</v>
+      </c>
+      <c r="U76" s="9">
+        <v>0.63636363636363635</v>
+      </c>
+      <c r="V76" s="9">
+        <v>0</v>
+      </c>
+      <c r="W76" s="9">
+        <v>0</v>
+      </c>
+      <c r="X76" s="9">
+        <v>0.090909090909090912</v>
+      </c>
+      <c r="Y76" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z76" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA76" s="9">
+        <v>0.54545454545454541</v>
+      </c>
+      <c r="AB76" s="9">
+        <v>0.060606060606060608</v>
+      </c>
+      <c r="AC76" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD76" s="6">
+        <v>23</v>
+      </c>
+      <c r="AE76" s="6">
+        <v>21</v>
+      </c>
+      <c r="AF76" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG76" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH76" s="6">
+        <v>3</v>
+      </c>
+      <c r="AI76" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ76" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK76" s="6">
+        <v>18</v>
+      </c>
+      <c r="AL76" s="6">
+        <v>2</v>
+      </c>
+      <c r="AM76" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN76" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO76" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP76" s="4">
         <v>58</v>
       </c>
@@ -28078,7 +28188,9 @@
       <c r="N179" s="6">
         <v>58</v>
       </c>
-      <c r="O179" s="6"/>
+      <c r="O179" s="6">
+        <v>29</v>
+      </c>
       <c r="P179" s="7">
         <v>5.0956140350877188</v>
       </c>
@@ -28088,31 +28200,75 @@
       <c r="R179" s="8">
         <v>2.7103448275862068</v>
       </c>
-      <c r="S179" s="8"/>
+      <c r="S179" s="8">
+        <v>7</v>
+      </c>
       <c r="T179" s="9">
         <v>0.48275862068965519</v>
       </c>
-      <c r="U179" s="9"/>
-      <c r="V179" s="9"/>
-      <c r="W179" s="9"/>
-      <c r="X179" s="9"/>
-      <c r="Y179" s="9"/>
-      <c r="Z179" s="9"/>
-      <c r="AA179" s="9"/>
-      <c r="AB179" s="9"/>
-      <c r="AC179" s="9"/>
-      <c r="AD179" s="6"/>
-      <c r="AE179" s="6"/>
-      <c r="AF179" s="6"/>
-      <c r="AG179" s="6"/>
-      <c r="AH179" s="6"/>
-      <c r="AI179" s="6"/>
-      <c r="AJ179" s="6"/>
-      <c r="AK179" s="6"/>
-      <c r="AL179" s="6"/>
-      <c r="AM179" s="6"/>
-      <c r="AN179" s="9"/>
-      <c r="AO179" s="6"/>
+      <c r="U179" s="9">
+        <v>0</v>
+      </c>
+      <c r="V179" s="9">
+        <v>0</v>
+      </c>
+      <c r="W179" s="9">
+        <v>0</v>
+      </c>
+      <c r="X179" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y179" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z179" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA179" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB179" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC179" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN179" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO179" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP179" s="4">
         <v>58</v>
       </c>
@@ -33325,10 +33481,10 @@
         <v>335</v>
       </c>
       <c t="s" r="AN216" s="11">
-        <v>336</v>
+        <v>319</v>
       </c>
       <c t="s" r="AO216" s="11">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="AP216" s="12"/>
       <c t="s" r="AQ216" s="12">
@@ -33345,10 +33501,10 @@
         <v>59</v>
       </c>
       <c t="s" r="AX216" s="11">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c t="s" r="AY216" s="11">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="AZ216" s="12"/>
       <c r="BA216" s="12"/>
